--- a/output/yearly_surface_area_iteration_71_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_71_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497636325652</v>
+        <v>10.8449763458653</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907205007274</v>
+        <v>37.78907198947343</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.955862411037899</v>
+        <v>4.6475936319044</v>
       </c>
       <c r="C2" t="n">
-        <v>9.192103754862885</v>
+        <v>7.278677479285853</v>
       </c>
       <c r="D2" t="n">
-        <v>22.69702517448201</v>
+        <v>31.79291765432871</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.48630927096744</v>
+        <v>13.54320958008475</v>
       </c>
       <c r="C3" t="n">
-        <v>27.59201922785661</v>
+        <v>39.93258787023902</v>
       </c>
       <c r="D3" t="n">
-        <v>78.41218913819274</v>
+        <v>92.83897165209963</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.75288698263284</v>
+        <v>30.63052837250048</v>
       </c>
       <c r="C4" t="n">
-        <v>68.7655361962636</v>
+        <v>106.7856795386298</v>
       </c>
       <c r="D4" t="n">
-        <v>84.73169911042947</v>
+        <v>111.1377671115559</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.38066573400307</v>
+        <v>40.34983064454391</v>
       </c>
       <c r="C5" t="n">
-        <v>117.4661128131309</v>
+        <v>151.7781950765569</v>
       </c>
       <c r="D5" t="n">
-        <v>56.57321145722246</v>
+        <v>77.18991324640548</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.19253002768617</v>
+        <v>37.55479493055324</v>
       </c>
       <c r="C6" t="n">
-        <v>142.812875041375</v>
+        <v>151.7487426454295</v>
       </c>
       <c r="D6" t="n">
-        <v>41.53970886209105</v>
+        <v>49.54978838104078</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.64954143177966</v>
+        <v>25.09248957284423</v>
       </c>
       <c r="C7" t="n">
-        <v>119.4139002583565</v>
+        <v>118.2161680591754</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>39.58504918293564</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.18625432636641</v>
+        <v>12.93452600345173</v>
       </c>
       <c r="C8" t="n">
-        <v>72.51679417419065</v>
+        <v>79.02578145334699</v>
       </c>
       <c r="D8" t="n">
-        <v>36.04977569994287</v>
+        <v>35.46563581591602</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.432811868852599</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>39.60468413702056</v>
+        <v>43.70937128847648</v>
       </c>
       <c r="D9" t="n">
-        <v>34.39062207976576</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.44952694202058</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.691626243298229</v>
+        <v>7.652707622317307</v>
       </c>
       <c r="C21" t="n">
-        <v>94.2224214804033</v>
+        <v>91.83249146780769</v>
       </c>
       <c r="D21" t="n">
-        <v>8.653079523710508</v>
+        <v>7.652707622317307</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.935646619876215</v>
+        <v>4.913647259755286</v>
       </c>
       <c r="C2" t="n">
-        <v>15.30151971839079</v>
+        <v>5.473243451175968</v>
       </c>
       <c r="D2" t="n">
-        <v>23.77007541522377</v>
+        <v>26.9774451649981</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.41620427333842</v>
+        <v>14.28442909679109</v>
       </c>
       <c r="C3" t="n">
-        <v>31.62700229231099</v>
+        <v>33.99792299806705</v>
       </c>
       <c r="D3" t="n">
-        <v>77.91149780902687</v>
+        <v>95.20989235785567</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.5486834601495</v>
+        <v>27.87378081897544</v>
       </c>
       <c r="C4" t="n">
-        <v>68.75277347610837</v>
+        <v>103.2248806153266</v>
       </c>
       <c r="D4" t="n">
-        <v>101.5912524354599</v>
+        <v>127.7548287536374</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.09305471438775</v>
+        <v>42.92691836819179</v>
       </c>
       <c r="C5" t="n">
-        <v>120.6813365445392</v>
+        <v>170.3086829942154</v>
       </c>
       <c r="D5" t="n">
-        <v>70.63674732055802</v>
+        <v>93.7569057555704</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>46.08814597586652</v>
+        <v>44.55858305264999</v>
       </c>
       <c r="C6" t="n">
-        <v>163.8644910635394</v>
+        <v>189.9073124140945</v>
       </c>
       <c r="D6" t="n">
-        <v>48.82525857530663</v>
+        <v>59.97496725243766</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.6743471662931</v>
+        <v>33.35684174719388</v>
       </c>
       <c r="C7" t="n">
-        <v>159.1786092711693</v>
+        <v>163.4904451882213</v>
       </c>
       <c r="D7" t="n">
-        <v>40.90255460203486</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.86213871524472</v>
+        <v>18.94282195344221</v>
       </c>
       <c r="C8" t="n">
-        <v>112.9058947269044</v>
+        <v>112.5721005074605</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21943812632832</v>
+        <v>37.80219535202343</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.53906160508951</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>62.56874468705769</v>
+        <v>67.67186925373262</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>38.43542262126263</v>
+        <v>39.71660337530471</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.16129402759952</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
         <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.42774856607789</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1304,7 +1304,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.871071225491775</v>
+        <v>7.81939049288047</v>
       </c>
       <c r="C21" t="n">
-        <v>102.3239259313931</v>
+        <v>99.69722878422598</v>
       </c>
       <c r="D21" t="n">
-        <v>9.838839031864719</v>
+        <v>8.796814304490528</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.08861933528947</v>
+        <v>5.586144437164351</v>
       </c>
       <c r="C2" t="n">
-        <v>9.626036240139976</v>
+        <v>8.361545197070084</v>
       </c>
       <c r="D2" t="n">
-        <v>20.65008121112741</v>
+        <v>32.1326023599981</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.2212373908208</v>
+        <v>14.78512042595696</v>
       </c>
       <c r="C3" t="n">
-        <v>44.23755155336128</v>
+        <v>28.12216298814988</v>
       </c>
       <c r="D3" t="n">
-        <v>77.83295799268713</v>
+        <v>93.70781837035805</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.48937768726719</v>
+        <v>26.73789872516188</v>
       </c>
       <c r="C4" t="n">
-        <v>72.47948776142927</v>
+        <v>94.09953570435253</v>
       </c>
       <c r="D4" t="n">
-        <v>112.0566829627309</v>
+        <v>138.743530807272</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.05655012288138</v>
+        <v>42.092432819582</v>
       </c>
       <c r="C5" t="n">
-        <v>123.0375310347315</v>
+        <v>176.2237129123025</v>
       </c>
       <c r="D5" t="n">
-        <v>86.44288535893166</v>
+        <v>110.42207303516</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.5284109157256</v>
+        <v>49.42903341341842</v>
       </c>
       <c r="C6" t="n">
-        <v>174.531179870181</v>
+        <v>222.6319086397535</v>
       </c>
       <c r="D6" t="n">
-        <v>56.714583126634</v>
+        <v>71.76870242355459</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>42.99858595060179</v>
+        <v>40.8426679920758</v>
       </c>
       <c r="C7" t="n">
-        <v>191.5173786490593</v>
+        <v>206.1297114790688</v>
       </c>
       <c r="D7" t="n">
-        <v>44.79518424937346</v>
+        <v>48.32849423695774</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.78836876870596</v>
+        <v>25.53525778745954</v>
       </c>
       <c r="C8" t="n">
-        <v>155.5481062608646</v>
+        <v>153.1280981698962</v>
       </c>
       <c r="D8" t="n">
-        <v>39.80496066868692</v>
+        <v>40.3056519978528</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.97656122828509</v>
+        <v>13.20156137900685</v>
       </c>
       <c r="C9" t="n">
-        <v>94.51874197406589</v>
+        <v>95.84999186102456</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.829437941368314</v>
+        <v>6.975317438673588</v>
       </c>
       <c r="C10" t="n">
-        <v>53.09782458418874</v>
+        <v>55.8025395093887</v>
       </c>
       <c r="D10" t="n">
-        <v>36.72718161587318</v>
+        <v>35.87306111317846</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>37.6716229073586</v>
+        <v>37.31623023842126</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>32.54493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
         <v>24.55547357862122</v>
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.034061708630759</v>
+        <v>7.9696546929014</v>
       </c>
       <c r="C21" t="n">
-        <v>110.4683484936729</v>
+        <v>106.5941315175562</v>
       </c>
       <c r="D21" t="n">
-        <v>11.04683484936729</v>
+        <v>9.962068366126751</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.28554971321558</v>
+        <v>5.179700887606172</v>
       </c>
       <c r="C2" t="n">
-        <v>6.621888265144736</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="D2" t="n">
-        <v>17.2669786222929</v>
+        <v>26.78502261496573</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.45747873464579</v>
+        <v>17.82853830912208</v>
       </c>
       <c r="C3" t="n">
-        <v>59.36137493728339</v>
+        <v>46.99135386377358</v>
       </c>
       <c r="D3" t="n">
-        <v>84.21922680881264</v>
+        <v>101.4636252339079</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.08776076077224</v>
+        <v>20.21614872585032</v>
       </c>
       <c r="C4" t="n">
-        <v>101.0807436292516</v>
+        <v>136.7397837429043</v>
       </c>
       <c r="D4" t="n">
-        <v>104.2076100672777</v>
+        <v>129.4777959745906</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.57514959043517</v>
+        <v>27.83254741539708</v>
       </c>
       <c r="C5" t="n">
-        <v>104.2861498836175</v>
+        <v>133.0268139254428</v>
       </c>
       <c r="D5" t="n">
-        <v>57.11317269455821</v>
+        <v>71.49577656177398</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.68684784454105</v>
+        <v>25.35854320069512</v>
       </c>
       <c r="C6" t="n">
-        <v>126.1486895094897</v>
+        <v>135.7688352634042</v>
       </c>
       <c r="D6" t="n">
-        <v>29.5044637557294</v>
+        <v>31.79880814055419</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.38518925743002</v>
+        <v>16.88802400845363</v>
       </c>
       <c r="C7" t="n">
-        <v>109.3529497852352</v>
+        <v>107.6761247063817</v>
       </c>
       <c r="D7" t="n">
-        <v>27.96704685087888</v>
+        <v>28.32636651063322</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>9.095892479846697</v>
       </c>
       <c r="C8" t="n">
-        <v>69.59609475405638</v>
+        <v>70.59747741238813</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>4.992187076095029</v>
       </c>
       <c r="C9" t="n">
-        <v>40.49218406165969</v>
+        <v>42.59999638267758</v>
       </c>
       <c r="D9" t="n">
-        <v>27.95624762613216</v>
+        <v>27.29062268265283</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.18597658892593</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>28.25371718051895</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>26.90381408717959</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
         <v>20.66578917439536</v>
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>16.24890625298896</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>71.95719798276996</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.367795536194059</v>
+        <v>3.168099841604457</v>
       </c>
       <c r="C2" t="n">
-        <v>3.081706043630738</v>
+        <v>2.756747553525043</v>
       </c>
       <c r="D2" t="n">
-        <v>12.2041057114921</v>
+        <v>18.4058059592192</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.28352946454486</v>
+        <v>18.20160243673586</v>
       </c>
       <c r="C3" t="n">
-        <v>43.13799412460485</v>
+        <v>35.89269606726339</v>
       </c>
       <c r="D3" t="n">
-        <v>80.46404184006859</v>
+        <v>99.93209881528283</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.66430870507238</v>
+        <v>25.89555919491812</v>
       </c>
       <c r="C4" t="n">
-        <v>126.4275058574957</v>
+        <v>131.3922039978719</v>
       </c>
       <c r="D4" t="n">
-        <v>118.5656702418873</v>
+        <v>147.3583669120378</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.20761609614836</v>
+        <v>30.23782929080177</v>
       </c>
       <c r="C5" t="n">
-        <v>144.292368831675</v>
+        <v>187.7837921298087</v>
       </c>
       <c r="D5" t="n">
-        <v>74.34284490408973</v>
+        <v>91.13073064671019</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.71830482880595</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C6" t="n">
-        <v>149.3336432929823</v>
+        <v>170.9890341532585</v>
       </c>
       <c r="D6" t="n">
-        <v>36.14598697495907</v>
+        <v>39.72838434775569</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>15.63040519931347</v>
       </c>
       <c r="C7" t="n">
-        <v>138.5776154452543</v>
+        <v>139.1764815448448</v>
       </c>
       <c r="D7" t="n">
-        <v>30.42239785920016</v>
+        <v>30.96137734883166</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.678649705541805</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>93.87962421860124</v>
+        <v>93.29548433457438</v>
       </c>
       <c r="D8" t="n">
-        <v>28.28906009787184</v>
+        <v>27.03733177495716</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>4.215624642035802</v>
       </c>
       <c r="C9" t="n">
-        <v>45.48437113775471</v>
+        <v>45.5953086283346</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>32.02951885105219</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.18245050873644</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
         <v>17.5585576904542</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>62.58837964114266</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.895574890451343</v>
+        <v>2.965859814529614</v>
       </c>
       <c r="C2" t="n">
-        <v>3.84746925294325</v>
+        <v>6.009277697694727</v>
       </c>
       <c r="D2" t="n">
-        <v>13.11418583332889</v>
+        <v>26.62205249606076</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.54168805303276</v>
+        <v>14.65258448588365</v>
       </c>
       <c r="C3" t="n">
-        <v>26.57591035396116</v>
+        <v>22.97289627937536</v>
       </c>
       <c r="D3" t="n">
-        <v>72.4088019267235</v>
+        <v>93.09913479372503</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.77314383152353</v>
+        <v>29.62227348023901</v>
       </c>
       <c r="C4" t="n">
-        <v>116.8044148604685</v>
+        <v>110.7421227867444</v>
       </c>
       <c r="D4" t="n">
-        <v>129.74581309785</v>
+        <v>158.7299505703286</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.63806355896497</v>
+        <v>34.11573272257667</v>
       </c>
       <c r="C5" t="n">
-        <v>189.1582389157542</v>
+        <v>214.9536598448392</v>
       </c>
       <c r="D5" t="n">
-        <v>95.67131377885168</v>
+        <v>117.8833555874358</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.51454327467913</v>
+        <v>34.57617239586842</v>
       </c>
       <c r="C6" t="n">
-        <v>186.4456700089203</v>
+        <v>227.2608490652772</v>
       </c>
       <c r="D6" t="n">
-        <v>48.02022545782425</v>
+        <v>54.98376192404687</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.51169584255761</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="C7" t="n">
-        <v>175.8869734497458</v>
+        <v>187.8642954415569</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>34.49468733641593</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.35038611942487</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>134.6025189907589</v>
+        <v>132.5997536740954</v>
       </c>
       <c r="D8" t="n">
-        <v>29.79113408536946</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>75.43749359432489</v>
+        <v>73.66249374504666</v>
       </c>
       <c r="D9" t="n">
-        <v>29.84218496599028</v>
+        <v>28.84374755077128</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>41.56719779780995</v>
+        <v>40.85543071223102</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.34073287329842</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.21141991377833</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
+        <v>14.05273663858884</v>
+      </c>
+      <c r="D16" t="n">
         <v>14.87936820556466</v>
-      </c>
-      <c r="D16" t="n">
-        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.34245002233289</v>
+        <v>1.790707812546182</v>
       </c>
       <c r="C2" t="n">
-        <v>1.806415775814131</v>
+        <v>2.969786805346601</v>
       </c>
       <c r="D2" t="n">
-        <v>9.185231520933158</v>
+        <v>18.54128714240526</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.84464718301752</v>
+        <v>14.31388152791849</v>
       </c>
       <c r="C3" t="n">
-        <v>23.30178176029805</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D3" t="n">
-        <v>70.0722423906161</v>
+        <v>96.06401286055041</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.65301075870693</v>
+        <v>32.40454647407447</v>
       </c>
       <c r="C4" t="n">
-        <v>111.1377671115559</v>
+        <v>104.4501017502267</v>
       </c>
       <c r="D4" t="n">
-        <v>137.5565978328376</v>
+        <v>169.0932793363579</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.76707341884881</v>
+        <v>35.88287859022093</v>
       </c>
       <c r="C5" t="n">
-        <v>224.4766125760332</v>
+        <v>249.8547907308133</v>
       </c>
       <c r="D5" t="n">
-        <v>101.2672756930585</v>
+        <v>120.7058802371454</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.07427833482005</v>
+        <v>27.81389420901639</v>
       </c>
       <c r="C6" t="n">
-        <v>224.84574971283</v>
+        <v>258.3351274000972</v>
       </c>
       <c r="D6" t="n">
-        <v>47.33594730796422</v>
+        <v>53.09193409796327</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.144578954431539</v>
+        <v>7.186393195086651</v>
       </c>
       <c r="C7" t="n">
-        <v>180.7976754663884</v>
+        <v>185.828150702949</v>
       </c>
       <c r="D7" t="n">
-        <v>33.65627479698915</v>
+        <v>34.31502750653876</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.088979188187965</v>
+        <v>3.67173641388307</v>
       </c>
       <c r="C8" t="n">
-        <v>96.46652941929158</v>
+        <v>91.96030745679872</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>31.8390597964283</v>
+        <v>30.84062238120929</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.33890824661018</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>19.19120412261664</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.92282714645877</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>14.75370449942107</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>11.82515109765283</v>
+      </c>
+      <c r="D15" t="n">
         <v>12.541826921753</v>
-      </c>
-      <c r="D15" t="n">
-        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.104286240828415</v>
+        <v>1.805434028109884</v>
       </c>
       <c r="C2" t="n">
-        <v>7.81765696891735</v>
+        <v>8.19366633964388</v>
       </c>
       <c r="D2" t="n">
-        <v>13.71403368062369</v>
+        <v>14.06451761103981</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.63156687346696</v>
+        <v>10.47524800431347</v>
       </c>
       <c r="C3" t="n">
-        <v>15.0207398749762</v>
+        <v>18.09851892778995</v>
       </c>
       <c r="D3" t="n">
-        <v>62.74840451693489</v>
+        <v>89.32922360941728</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.89626320518188</v>
+        <v>29.94134148411922</v>
       </c>
       <c r="C4" t="n">
-        <v>86.11007288719199</v>
+        <v>84.73169911042947</v>
       </c>
       <c r="D4" t="n">
-        <v>140.2240063452762</v>
+        <v>176.3425043845163</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.43728830567989</v>
+        <v>41.25794727097221</v>
       </c>
       <c r="C5" t="n">
-        <v>217.2116795646068</v>
+        <v>226.3419332141022</v>
       </c>
       <c r="D5" t="n">
-        <v>121.6876279413922</v>
+        <v>147.6303110261141</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.09064925062275</v>
+        <v>35.58246379272141</v>
       </c>
       <c r="C6" t="n">
-        <v>284.1766904712818</v>
+        <v>318.2295913407867</v>
       </c>
       <c r="D6" t="n">
-        <v>62.67182819600364</v>
+        <v>70.48064943558278</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.42700349808513</v>
+        <v>14.85187926984575</v>
       </c>
       <c r="C7" t="n">
-        <v>242.7204301640517</v>
+        <v>261.464939081236</v>
       </c>
       <c r="D7" t="n">
-        <v>38.26754376383641</v>
+        <v>39.16584291322225</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>155.6315548157256</v>
+        <v>150.9584357435108</v>
       </c>
       <c r="D8" t="n">
-        <v>33.29597338953057</v>
+        <v>32.71183350550372</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>62.56874468705769</v>
+        <v>59.68436993198057</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.81130881880213</v>
+        <v>22.21204180858408</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.00819813899924</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.04572553593887</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>13.82791641431633</v>
+      </c>
+      <c r="D14" t="n">
         <v>14.13520344574558</v>
-      </c>
-      <c r="D14" t="n">
-        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.060688431214055</v>
+        <v>1.290998231084556</v>
       </c>
       <c r="C2" t="n">
-        <v>4.614214209960009</v>
+        <v>4.448298847942298</v>
       </c>
       <c r="D2" t="n">
-        <v>9.921542299118265</v>
+        <v>10.13556329864407</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.47310458245573</v>
+        <v>8.806276907093888</v>
       </c>
       <c r="C3" t="n">
-        <v>22.11877577668064</v>
+        <v>24.18535469412017</v>
       </c>
       <c r="D3" t="n">
-        <v>60.63273821428301</v>
+        <v>82.48153337229577</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.56970107256619</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="C4" t="n">
-        <v>67.82109490477815</v>
+        <v>70.93519862264904</v>
       </c>
       <c r="D4" t="n">
-        <v>140.1601927445001</v>
+        <v>179.6480489047154</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.37057051952011</v>
+        <v>43.73686022419541</v>
       </c>
       <c r="C5" t="n">
-        <v>202.6818135417541</v>
+        <v>206.8296975921968</v>
       </c>
       <c r="D5" t="n">
-        <v>134.7694161004809</v>
+        <v>166.1853426363789</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.05418571684538</v>
+        <v>40.65417243286043</v>
       </c>
       <c r="C6" t="n">
-        <v>317.666068158549</v>
+        <v>347.0095252907819</v>
       </c>
       <c r="D6" t="n">
-        <v>75.5523580757218</v>
+        <v>84.20646408865744</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.75017841923158</v>
+        <v>13.1750541909922</v>
       </c>
       <c r="C7" t="n">
-        <v>301.5889677538032</v>
+        <v>327.0407769864017</v>
       </c>
       <c r="D7" t="n">
-        <v>42.33983324105218</v>
+        <v>43.77711188006952</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>3.838633523605028</v>
       </c>
       <c r="C8" t="n">
-        <v>198.4406634594078</v>
+        <v>196.5213466976053</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>71.44374393344886</v>
+        <v>65.78593191387449</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>31.61718481526852</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>30.32127784566274</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>24.76949457814703</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>23.81130881880213</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.079742548222244</v>
+        <v>1.795616551067416</v>
       </c>
       <c r="C2" t="n">
-        <v>9.837111996553039</v>
+        <v>15.55481062608646</v>
       </c>
       <c r="D2" t="n">
-        <v>15.6834195753428</v>
+        <v>13.21137885604933</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.871473166201678</v>
+        <v>6.75933294373929</v>
       </c>
       <c r="C3" t="n">
-        <v>20.00801821255</v>
+        <v>20.93576979306323</v>
       </c>
       <c r="D3" t="n">
-        <v>55.42456664325368</v>
+        <v>73.76852249710534</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.96686692442964</v>
+        <v>22.20713307006285</v>
       </c>
       <c r="C4" t="n">
-        <v>62.0523453946239</v>
+        <v>66.20022944506667</v>
       </c>
       <c r="D4" t="n">
-        <v>138.4117000832366</v>
+        <v>178.8567602550924</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.51154127830416</v>
+        <v>42.77965621255477</v>
       </c>
       <c r="C5" t="n">
-        <v>169.3269352899686</v>
+        <v>175.4874021341174</v>
       </c>
       <c r="D5" t="n">
-        <v>148.7838645786041</v>
+        <v>181.8933059043278</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.27810630887167</v>
+        <v>47.01393406097126</v>
       </c>
       <c r="C6" t="n">
-        <v>320.6446906932338</v>
+        <v>341.3742934684052</v>
       </c>
       <c r="D6" t="n">
-        <v>92.73981513397071</v>
+        <v>106.6266364105418</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.98511922018283</v>
+        <v>23.89475737366311</v>
       </c>
       <c r="C7" t="n">
-        <v>368.0631048083547</v>
+        <v>393.6346872608714</v>
       </c>
       <c r="D7" t="n">
-        <v>50.12509253572939</v>
+        <v>52.87987659384594</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>6.67588438887831</v>
       </c>
       <c r="C8" t="n">
-        <v>274.3788483828986</v>
+        <v>284.7264691856599</v>
       </c>
       <c r="D8" t="n">
-        <v>36.55046702910875</v>
+        <v>36.46701847424777</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>134.2343636016663</v>
+        <v>125.6921768270148</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>49.68134257340984</v>
+        <v>45.41074005993622</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.05067533218912</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>28.07602084605028</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.52848336452105</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3767,7 +3767,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.309291584566751</v>
+        <v>4.117449871611123</v>
       </c>
       <c r="C2" t="n">
-        <v>6.184028789050658</v>
+        <v>8.567712214961913</v>
       </c>
       <c r="D2" t="n">
-        <v>7.609526455617027</v>
+        <v>8.092546326106458</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.226603793231766</v>
+        <v>1.311614932873739</v>
       </c>
       <c r="C2" t="n">
-        <v>5.665666001208343</v>
+        <v>9.207811718130834</v>
       </c>
       <c r="D2" t="n">
-        <v>11.66807146497334</v>
+        <v>9.830239762623313</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.37140373184156</v>
+        <v>9.311876974780997</v>
       </c>
       <c r="C3" t="n">
-        <v>28.30378631343554</v>
+        <v>34.91094836301658</v>
       </c>
       <c r="D3" t="n">
-        <v>61.17269945161876</v>
+        <v>79.79645340118076</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.49160322458295</v>
+        <v>31.68983414538279</v>
       </c>
       <c r="C4" t="n">
-        <v>92.45314480433062</v>
+        <v>97.74967366874218</v>
       </c>
       <c r="D4" t="n">
-        <v>142.1384143685574</v>
+        <v>180.6563037969768</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.25670348136071</v>
+        <v>26.87534340375644</v>
       </c>
       <c r="C5" t="n">
-        <v>264.090132442392</v>
+        <v>276.7546778271759</v>
       </c>
       <c r="D5" t="n">
-        <v>134.8185034856933</v>
+        <v>163.4364490644878</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>17.99249017573129</v>
+        <v>14.81260936167588</v>
       </c>
       <c r="C6" t="n">
-        <v>302.1289289911389</v>
+        <v>319.4773926728844</v>
       </c>
       <c r="D6" t="n">
-        <v>74.14355012012763</v>
+        <v>81.8316163920844</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>4.371722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>192.9546572880766</v>
+        <v>200.2009370931223</v>
       </c>
       <c r="D7" t="n">
-        <v>32.03933632809466</v>
+        <v>31.85967649821749</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.668971097219577</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>98.88653751025997</v>
+        <v>92.62789589568656</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.94062177832222</v>
+        <v>34.61249706092553</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>19.85781081380023</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.92242623583128</v>
+        <v>20.35653864755762</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>18.79065105928395</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.84831213192725</v>
+        <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
         <v>9.105709956889166</v>
@@ -4375,7 +4375,7 @@
         <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.65030219530566</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.810964661436871</v>
+        <v>7.063674732055801</v>
       </c>
       <c r="C2" t="n">
-        <v>5.221916038888784</v>
+        <v>7.152032025438014</v>
       </c>
       <c r="D2" t="n">
-        <v>8.728718838458391</v>
+        <v>28.82902133520759</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.28028112179585</v>
+        <v>8.752280783360314</v>
       </c>
       <c r="C3" t="n">
-        <v>15.58033606639688</v>
+        <v>21.58863201638736</v>
       </c>
       <c r="D3" t="n">
-        <v>9.527861469715296</v>
+        <v>9.935286766977722</v>
       </c>
     </row>
     <row r="4">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39872305039215</v>
+        <v>13.39843513116856</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14625596970008</v>
+        <v>70.14474862788245</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576320358869665</v>
+        <v>1.57628648601983</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.067380738694535</v>
+        <v>4.385466994870503</v>
       </c>
       <c r="C2" t="n">
-        <v>10.12672756930585</v>
+        <v>4.671155576806324</v>
       </c>
       <c r="D2" t="n">
-        <v>16.47274472955723</v>
+        <v>22.91202792171206</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.56208377064369</v>
+        <v>18.05924901962008</v>
       </c>
       <c r="C3" t="n">
-        <v>18.63357142660446</v>
+        <v>25.53034904893831</v>
       </c>
       <c r="D3" t="n">
-        <v>14.55440971545896</v>
+        <v>31.74972075534185</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>13.17112720017521</v>
+        <v>10.3250406055637</v>
       </c>
       <c r="C4" t="n">
-        <v>24.65757533986289</v>
+        <v>33.43832680664636</v>
       </c>
       <c r="D4" t="n">
-        <v>20.06299608398782</v>
+        <v>20.27996232662636</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.366053024963819</v>
+        <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.42267559664065</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4893,7 +4893,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.641744203407924</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4949,7 +4949,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.463246047684251</v>
+        <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
         <v>29.49759152179966</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4983,7 +4983,7 @@
         <v>26.79680358741669</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>44.74806035956962</v>
       </c>
     </row>
     <row r="14">
@@ -4997,7 +4997,7 @@
         <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>44.86390658867074</v>
       </c>
     </row>
     <row r="15">
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44435323741262</v>
+        <v>15.43885238644461</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16323385082831</v>
+        <v>86.13254489279623</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25144278682371</v>
+        <v>3.250284712935707</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.713370728088937</v>
+        <v>5.133558745506572</v>
       </c>
       <c r="C2" t="n">
-        <v>7.890306299031615</v>
+        <v>9.72028401974767</v>
       </c>
       <c r="D2" t="n">
-        <v>17.35533591567511</v>
+        <v>25.95544580487717</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.16800203061322</v>
+        <v>16.43936530761284</v>
       </c>
       <c r="C3" t="n">
-        <v>31.22939447209104</v>
+        <v>21.31374265919825</v>
       </c>
       <c r="D3" t="n">
-        <v>24.35225180384213</v>
+        <v>42.71093387325749</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.80247308946392</v>
+        <v>24.26193101505142</v>
       </c>
       <c r="C4" t="n">
-        <v>37.61173629739955</v>
+        <v>50.75733805726435</v>
       </c>
       <c r="D4" t="n">
-        <v>22.85803179797848</v>
+        <v>31.61325782445154</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.87914722138641</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="C5" t="n">
-        <v>28.2252464970958</v>
+        <v>37.52730599483434</v>
       </c>
       <c r="D5" t="n">
-        <v>29.64878066825368</v>
+        <v>29.96784867213389</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.876741757621407</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.27675504160637</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.19419042345839</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -5224,7 +5224,7 @@
         <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5232,10 +5232,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
         <v>41.26874649571891</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5308,7 +5308,7 @@
         <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.35888735806038</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5336,7 +5336,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
         <v>24.67426505083508</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74132543371212</v>
+        <v>16.72915241538278</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1220851456439</v>
+        <v>102.0478297338349</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022397630113636</v>
+        <v>4.182288103845694</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.905793278121311</v>
+        <v>5.324017800130453</v>
       </c>
       <c r="C2" t="n">
-        <v>7.585964510715104</v>
+        <v>13.80140922630166</v>
       </c>
       <c r="D2" t="n">
-        <v>23.89181213055037</v>
+        <v>25.68153819539231</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.70796326794897</v>
+        <v>17.00877897607599</v>
       </c>
       <c r="C3" t="n">
-        <v>31.1803070868787</v>
+        <v>30.77288178961627</v>
       </c>
       <c r="D3" t="n">
-        <v>32.12278488295564</v>
+        <v>52.93583621298801</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.73789872516188</v>
+        <v>28.1162725019244</v>
       </c>
       <c r="C4" t="n">
-        <v>59.89544568839366</v>
+        <v>52.19952543480291</v>
       </c>
       <c r="D4" t="n">
-        <v>29.31596819651401</v>
+        <v>45.12897846881738</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>24.07736244665303</v>
+        <v>22.85017781634452</v>
       </c>
       <c r="C5" t="n">
-        <v>50.90361846519713</v>
+        <v>67.88785374866696</v>
       </c>
       <c r="D5" t="n">
-        <v>31.34229545807943</v>
+        <v>34.09118902997049</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.98870205363455</v>
+        <v>9.338384162795663</v>
       </c>
       <c r="C6" t="n">
-        <v>29.38370878810704</v>
+        <v>36.58875518957439</v>
       </c>
       <c r="D6" t="n">
-        <v>38.15856976866503</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.62700229231099</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.87187407682917</v>
+        <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5560,10 +5560,10 @@
         <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.59540643932586</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.7623035490478</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.06370009425158</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>44.07556318216055</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>41.74489413227862</v>
       </c>
     </row>
     <row r="17">
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07160950675544</v>
+        <v>18.04925915946834</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8957382107379</v>
+        <v>117.7499288022458</v>
       </c>
       <c r="D21" t="n">
-        <v>6.884422669240169</v>
+        <v>6.016419719822779</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.450082416901544</v>
+        <v>4.993168823799278</v>
       </c>
       <c r="C2" t="n">
-        <v>7.004769869800992</v>
+        <v>11.60523961190155</v>
       </c>
       <c r="D2" t="n">
-        <v>36.54654003829177</v>
+        <v>37.6107545496953</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.52986602285279</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="C3" t="n">
-        <v>28.36759991421159</v>
+        <v>40.92906179004953</v>
       </c>
       <c r="D3" t="n">
-        <v>40.57563261652067</v>
+        <v>57.08862900195202</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.82875929330033</v>
+        <v>22.14331946928681</v>
       </c>
       <c r="C4" t="n">
-        <v>58.1724784674405</v>
+        <v>54.62444226429253</v>
       </c>
       <c r="D4" t="n">
-        <v>33.17030968338698</v>
+        <v>52.90147504333937</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.70858516275472</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="C5" t="n">
-        <v>62.12008598621694</v>
+        <v>61.8255616749429</v>
       </c>
       <c r="D5" t="n">
-        <v>28.32342126752049</v>
+        <v>33.87029579651497</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>12.07549676223577</v>
+        <v>10.98870205363455</v>
       </c>
       <c r="C6" t="n">
-        <v>37.95731148929444</v>
+        <v>49.50953672516665</v>
       </c>
       <c r="D6" t="n">
-        <v>30.75226508782709</v>
+        <v>31.23528495831652</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.449681506274044</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C7" t="n">
-        <v>20.66088043587412</v>
+        <v>23.53543771390878</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
         <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.96562313481813</v>
+        <v>21.74374815365835</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.39687241888974</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.17892442854696</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5930,7 +5930,7 @@
         <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>29.49955501720816</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.064249388807356</v>
+        <v>7.051197722815141</v>
       </c>
       <c r="C21" t="n">
-        <v>66.22733802006896</v>
+        <v>66.10497865139195</v>
       </c>
       <c r="D21" t="n">
-        <v>5.298187041605517</v>
+        <v>4.406998576759463</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.524294331796802</v>
+        <v>4.693735774004001</v>
       </c>
       <c r="C2" t="n">
-        <v>7.354272052512856</v>
+        <v>12.17956201888593</v>
       </c>
       <c r="D2" t="n">
-        <v>30.50780990946964</v>
+        <v>38.02014334236623</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.48769192929919</v>
+        <v>16.87133429748144</v>
       </c>
       <c r="C3" t="n">
-        <v>27.72455516792992</v>
+        <v>43.707407793068</v>
       </c>
       <c r="D3" t="n">
-        <v>61.4672237628928</v>
+        <v>74.8877148799467</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.74240655305561</v>
+        <v>27.70786545695773</v>
       </c>
       <c r="C4" t="n">
-        <v>65.81734784041041</v>
+        <v>84.31052934530759</v>
       </c>
       <c r="D4" t="n">
-        <v>46.41801320449344</v>
+        <v>70.53955429783758</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.50718801466389</v>
+        <v>27.63619787454772</v>
       </c>
       <c r="C5" t="n">
-        <v>90.41896356113125</v>
+        <v>85.41205026947252</v>
       </c>
       <c r="D5" t="n">
-        <v>34.60660657470007</v>
+        <v>45.52854978444584</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.7296027751714</v>
+        <v>19.76356303419254</v>
       </c>
       <c r="C6" t="n">
-        <v>74.26430508774999</v>
+        <v>77.76619914879835</v>
       </c>
       <c r="D6" t="n">
-        <v>33.00635781677777</v>
+        <v>35.42145716922493</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.65981657271187</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>40.96244121199391</v>
+        <v>50.783845245279</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>33.35684174719388</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.674501730546564</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>24.20008090968387</v>
+        <v>26.28629478120835</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.17343485294896</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6193,7 +6193,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.909319358310797</v>
       </c>
       <c r="C11" t="n">
         <v>23.27821981539612</v>
@@ -6213,7 +6213,7 @@
         <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6252,10 +6252,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.287200296280024</v>
+        <v>7.267879287466918</v>
       </c>
       <c r="C21" t="n">
-        <v>75.60470307390526</v>
+        <v>75.40424760746927</v>
       </c>
       <c r="D21" t="n">
-        <v>6.376300259245021</v>
+        <v>5.450909465600188</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.250386722311942</v>
+        <v>3.232895190084747</v>
       </c>
       <c r="C2" t="n">
-        <v>6.996915888167017</v>
+        <v>9.051713833155592</v>
       </c>
       <c r="D2" t="n">
-        <v>30.61383866152829</v>
+        <v>33.69063596663779</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.29134238844982</v>
+        <v>16.43936530761284</v>
       </c>
       <c r="C3" t="n">
-        <v>28.26451640526567</v>
+        <v>45.80834788015617</v>
       </c>
       <c r="D3" t="n">
-        <v>71.60867754776235</v>
+        <v>87.12520001338319</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.55769911593697</v>
+        <v>30.31146036862027</v>
       </c>
       <c r="C4" t="n">
-        <v>67.98701026679586</v>
+        <v>98.60477591914113</v>
       </c>
       <c r="D4" t="n">
-        <v>66.77455185205106</v>
+        <v>90.36005869887643</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.45305302221007</v>
+        <v>35.17111150464198</v>
       </c>
       <c r="C5" t="n">
-        <v>108.3113154710294</v>
+        <v>124.1419972020092</v>
       </c>
       <c r="D5" t="n">
-        <v>43.17235529425349</v>
+        <v>60.57383335202821</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.18245050873644</v>
+        <v>28.82018560586937</v>
       </c>
       <c r="C6" t="n">
-        <v>111.738596706555</v>
+        <v>107.8341860867654</v>
       </c>
       <c r="D6" t="n">
-        <v>36.87051678069322</v>
+        <v>41.70071548558752</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.1456428175938</v>
+        <v>16.88802400845363</v>
       </c>
       <c r="C7" t="n">
-        <v>77.73281972685395</v>
+        <v>83.8412539426776</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.92899537012474</v>
+        <v>8.011061266653972</v>
       </c>
       <c r="C8" t="n">
-        <v>40.88979188187965</v>
+        <v>48.06636759992384</v>
       </c>
       <c r="D8" t="n">
-        <v>34.46425315758427</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,10 +6476,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>27.62343515439249</v>
+        <v>28.51093507903161</v>
       </c>
       <c r="D9" t="n">
         <v>32.72655972106742</v>
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
         <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6538,7 +6538,7 @@
         <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>17.3592629064921</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>18.82992096745382</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.496939436511081</v>
+        <v>7.468681007003165</v>
       </c>
       <c r="C21" t="n">
-        <v>85.27768609031354</v>
+        <v>84.0226613287856</v>
       </c>
       <c r="D21" t="n">
-        <v>7.496939436511081</v>
+        <v>6.535095881127769</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_71_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_71_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449763458653</v>
+        <v>10.84497637740282</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907198947343</v>
+        <v>37.7890720993652</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.6475936319044</v>
+        <v>5.097234080449439</v>
       </c>
       <c r="C2" t="n">
-        <v>7.278677479285853</v>
+        <v>8.089601082993719</v>
       </c>
       <c r="D2" t="n">
-        <v>31.79291765432871</v>
+        <v>25.26429542108742</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.54320958008475</v>
+        <v>17.18549356284042</v>
       </c>
       <c r="C3" t="n">
-        <v>39.93258787023902</v>
+        <v>27.26313374693393</v>
       </c>
       <c r="D3" t="n">
-        <v>92.83897165209963</v>
+        <v>94.36068059368218</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.63052837250048</v>
+        <v>32.1492920709703</v>
       </c>
       <c r="C4" t="n">
-        <v>106.7856795386298</v>
+        <v>63.09888844735099</v>
       </c>
       <c r="D4" t="n">
-        <v>111.1377671115559</v>
+        <v>125.1384711218197</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.34983064454391</v>
+        <v>42.65693774952392</v>
       </c>
       <c r="C5" t="n">
-        <v>151.7781950765569</v>
+        <v>102.3717418603362</v>
       </c>
       <c r="D5" t="n">
-        <v>77.18991324640548</v>
+        <v>92.25974050659401</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.55479493055324</v>
+        <v>40.65417243286043</v>
       </c>
       <c r="C6" t="n">
-        <v>151.7487426454295</v>
+        <v>110.2895370950867</v>
       </c>
       <c r="D6" t="n">
-        <v>49.54978838104078</v>
+        <v>56.79508643838223</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.09248957284423</v>
+        <v>26.82920126165683</v>
       </c>
       <c r="C7" t="n">
-        <v>118.2161680591754</v>
+        <v>95.93834915440679</v>
       </c>
       <c r="D7" t="n">
-        <v>39.58504918293564</v>
+        <v>42.10028680121597</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.93452600345173</v>
+        <v>13.76901155206151</v>
       </c>
       <c r="C8" t="n">
-        <v>79.02578145334699</v>
+        <v>62.75331325545612</v>
       </c>
       <c r="D8" t="n">
-        <v>35.46563581591602</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>7.21093688769282</v>
       </c>
       <c r="C9" t="n">
-        <v>43.70937128847648</v>
+        <v>38.2734342500619</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>34.44952694202058</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.77167905773377</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -982,7 +982,7 @@
         <v>18.59921025695582</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -1007,7 +1007,7 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.652707622317307</v>
+        <v>7.669711798276759</v>
       </c>
       <c r="C21" t="n">
-        <v>91.83249146780769</v>
+        <v>92.9952555541057</v>
       </c>
       <c r="D21" t="n">
-        <v>7.652707622317307</v>
+        <v>7.669711798276759</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.913647259755286</v>
+        <v>6.263550353094651</v>
       </c>
       <c r="C2" t="n">
-        <v>5.473243451175968</v>
+        <v>10.81002397146163</v>
       </c>
       <c r="D2" t="n">
-        <v>26.9774451649981</v>
+        <v>37.48018210503048</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.28442909679109</v>
+        <v>16.99405276051229</v>
       </c>
       <c r="C3" t="n">
-        <v>33.99792299806705</v>
+        <v>29.20208546282137</v>
       </c>
       <c r="D3" t="n">
-        <v>95.20989235785567</v>
+        <v>92.36282401553993</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.87378081897544</v>
+        <v>32.03442758957343</v>
       </c>
       <c r="C4" t="n">
-        <v>103.2248806153266</v>
+        <v>64.83461838845936</v>
       </c>
       <c r="D4" t="n">
-        <v>127.7548287536374</v>
+        <v>140.9387186739679</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.92691836819179</v>
+        <v>45.50400609183966</v>
       </c>
       <c r="C5" t="n">
-        <v>170.3086829942154</v>
+        <v>108.973995171396</v>
       </c>
       <c r="D5" t="n">
-        <v>93.7569057555704</v>
+        <v>111.3547333541945</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.55858305264999</v>
+        <v>48.22148373719484</v>
       </c>
       <c r="C6" t="n">
-        <v>189.9073124140945</v>
+        <v>133.5549941903276</v>
       </c>
       <c r="D6" t="n">
-        <v>59.97496725243766</v>
+        <v>70.52090109145691</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.35684174719388</v>
+        <v>36.53083207502382</v>
       </c>
       <c r="C7" t="n">
-        <v>163.4904451882213</v>
+        <v>125.9415407438936</v>
       </c>
       <c r="D7" t="n">
-        <v>43.41779222031519</v>
+        <v>47.49008169753095</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.94282195344221</v>
+        <v>20.69524160552276</v>
       </c>
       <c r="C8" t="n">
-        <v>112.5721005074605</v>
+        <v>91.96030745679872</v>
       </c>
       <c r="D8" t="n">
-        <v>37.80219535202343</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>10.31718662392973</v>
       </c>
       <c r="C9" t="n">
-        <v>67.67186925373262</v>
+        <v>56.79999517690344</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.27812200440487</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>6.121196935978863</v>
       </c>
       <c r="C10" t="n">
-        <v>39.71660337530471</v>
+        <v>37.15424186722054</v>
       </c>
       <c r="D10" t="n">
-        <v>35.16129402759952</v>
+        <v>35.58835427894688</v>
       </c>
     </row>
     <row r="11">
@@ -1237,7 +1237,7 @@
         <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.79943003535993</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>27.83745615391831</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.81939049288047</v>
+        <v>7.847197723517082</v>
       </c>
       <c r="C21" t="n">
-        <v>99.69722878422598</v>
+        <v>101.0326706902824</v>
       </c>
       <c r="D21" t="n">
-        <v>8.796814304490528</v>
+        <v>8.828097438956718</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.586144437164351</v>
+        <v>7.496625469628643</v>
       </c>
       <c r="C2" t="n">
-        <v>8.361545197070084</v>
+        <v>10.36725575684632</v>
       </c>
       <c r="D2" t="n">
-        <v>32.1326023599981</v>
+        <v>33.75935830593507</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.78512042595696</v>
+        <v>18.38813450054276</v>
       </c>
       <c r="C3" t="n">
-        <v>28.12216298814988</v>
+        <v>34.87658719336794</v>
       </c>
       <c r="D3" t="n">
-        <v>93.70781837035805</v>
+        <v>97.85570242080082</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.73789872516188</v>
+        <v>31.396291581813</v>
       </c>
       <c r="C4" t="n">
-        <v>94.09953570435253</v>
+        <v>68.26779011021046</v>
       </c>
       <c r="D4" t="n">
-        <v>138.743530807272</v>
+        <v>149.579080219044</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.092432819582</v>
+        <v>46.2157731774186</v>
       </c>
       <c r="C5" t="n">
-        <v>176.2237129123025</v>
+        <v>112.1401315175919</v>
       </c>
       <c r="D5" t="n">
-        <v>110.42207303516</v>
+        <v>130.9406000539184</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.42903341341842</v>
+        <v>53.53470231257858</v>
       </c>
       <c r="C6" t="n">
-        <v>222.6319086397535</v>
+        <v>149.2531399812341</v>
       </c>
       <c r="D6" t="n">
-        <v>71.76870242355459</v>
+        <v>83.96495415341272</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.8426679920758</v>
+        <v>45.15450390912779</v>
       </c>
       <c r="C7" t="n">
-        <v>206.1297114790688</v>
+        <v>155.1063197939536</v>
       </c>
       <c r="D7" t="n">
-        <v>48.32849423695774</v>
+        <v>54.85613472249477</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.53525778745954</v>
+        <v>28.70630287217673</v>
       </c>
       <c r="C8" t="n">
-        <v>153.1280981698962</v>
+        <v>122.9197213102219</v>
       </c>
       <c r="D8" t="n">
-        <v>40.3056519978528</v>
+        <v>41.72427743048944</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.20156137900685</v>
+        <v>14.53281126596553</v>
       </c>
       <c r="C9" t="n">
-        <v>95.84999186102456</v>
+        <v>80.54061816099981</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>36.94218436310322</v>
       </c>
     </row>
     <row r="10">
@@ -1514,10 +1514,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.975317438673588</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>55.8025395093887</v>
+        <v>49.96604940764142</v>
       </c>
       <c r="D10" t="n">
         <v>35.87306111317846</v>
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>5.153193699591506</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>36.60544490054656</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.54493639578176</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>36.23336252063703</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>31.34327720578367</v>
       </c>
     </row>
     <row r="15">
@@ -1587,7 +1587,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>21.90573652485908</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.9696546929014</v>
+        <v>8.008434941058676</v>
       </c>
       <c r="C21" t="n">
-        <v>106.5941315175562</v>
+        <v>109.1149260719244</v>
       </c>
       <c r="D21" t="n">
-        <v>9.962068366126751</v>
+        <v>10.01054367632334</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.179700887606172</v>
+        <v>6.819219553698344</v>
       </c>
       <c r="C2" t="n">
-        <v>5.885577486959628</v>
+        <v>7.132397071353077</v>
       </c>
       <c r="D2" t="n">
-        <v>26.78502261496573</v>
+        <v>27.9464301490897</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.82853830912208</v>
+        <v>21.87824758914017</v>
       </c>
       <c r="C3" t="n">
-        <v>46.99135386377358</v>
+        <v>50.1231290403209</v>
       </c>
       <c r="D3" t="n">
-        <v>101.4636252339079</v>
+        <v>106.9172337309989</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.21614872585032</v>
+        <v>22.19437034990764</v>
       </c>
       <c r="C4" t="n">
-        <v>136.7397837429043</v>
+        <v>93.33377249504001</v>
       </c>
       <c r="D4" t="n">
-        <v>129.4777959745906</v>
+        <v>144.7037211197544</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.83254741539708</v>
+        <v>30.13965452037709</v>
       </c>
       <c r="C5" t="n">
-        <v>133.0268139254428</v>
+        <v>89.16723523821656</v>
       </c>
       <c r="D5" t="n">
-        <v>71.49577656177398</v>
+        <v>85.36296288426017</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>25.35854320069512</v>
+        <v>28.01515248838698</v>
       </c>
       <c r="C6" t="n">
-        <v>135.7688352634042</v>
+        <v>102.1587026085146</v>
       </c>
       <c r="D6" t="n">
-        <v>31.79880814055419</v>
+        <v>36.10573531908495</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.88802400845363</v>
+        <v>18.98405535702057</v>
       </c>
       <c r="C7" t="n">
-        <v>107.6761247063817</v>
+        <v>86.41637817091699</v>
       </c>
       <c r="D7" t="n">
-        <v>28.32636651063322</v>
+        <v>29.34443887993716</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>10.09727513817844</v>
       </c>
       <c r="C8" t="n">
-        <v>70.59747741238813</v>
+        <v>59.33192250615598</v>
       </c>
       <c r="D8" t="n">
-        <v>26.53664044579129</v>
+        <v>27.20422888467911</v>
       </c>
     </row>
     <row r="9">
@@ -1811,10 +1811,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.992187076095029</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="C9" t="n">
-        <v>42.59999638267758</v>
+        <v>38.05155926890212</v>
       </c>
       <c r="D9" t="n">
         <v>27.29062268265283</v>
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>28.61303684027329</v>
       </c>
       <c r="D10" t="n">
-        <v>28.18597658892593</v>
+        <v>28.32833000604172</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.25371718051895</v>
+        <v>28.96450251839364</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
-        <v>26.90381408717959</v>
+        <v>26.68684784454105</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -1884,7 +1884,7 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="D14" t="n">
         <v>24.27567548291088</v>
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.27523351455437</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1968,7 +1968,7 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>71.95719798276996</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
         <v>6.724971774090649</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.168099841604457</v>
+        <v>4.019275101186442</v>
       </c>
       <c r="C2" t="n">
-        <v>2.756747553525043</v>
+        <v>3.316343744945725</v>
       </c>
       <c r="D2" t="n">
-        <v>18.4058059592192</v>
+        <v>19.14506198051705</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.20160243673586</v>
+        <v>23.2085157283946</v>
       </c>
       <c r="C3" t="n">
-        <v>35.89269606726339</v>
+        <v>39.56934121966769</v>
       </c>
       <c r="D3" t="n">
-        <v>99.93209881528283</v>
+        <v>106.2447365535898</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.89555919491812</v>
+        <v>30.6560538128109</v>
       </c>
       <c r="C4" t="n">
-        <v>131.3922039978719</v>
+        <v>112.0183948022653</v>
       </c>
       <c r="D4" t="n">
-        <v>147.3583669120378</v>
+        <v>160.8740875564036</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.23782929080177</v>
+        <v>33.30579086657305</v>
       </c>
       <c r="C5" t="n">
-        <v>187.7837921298087</v>
+        <v>127.9953569411779</v>
       </c>
       <c r="D5" t="n">
-        <v>91.13073064671019</v>
+        <v>108.4585776266664</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>29.82647700272235</v>
+        <v>33.20761609614837</v>
       </c>
       <c r="C6" t="n">
-        <v>170.9890341532585</v>
+        <v>122.204027233826</v>
       </c>
       <c r="D6" t="n">
-        <v>39.72838434775569</v>
+        <v>46.69192081397831</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.63040519931347</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="C7" t="n">
-        <v>139.1764815448448</v>
+        <v>111.329207913884</v>
       </c>
       <c r="D7" t="n">
-        <v>30.96137734883166</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.677267047210056</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>93.29548433457438</v>
+        <v>77.52370746584938</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>27.95526587842792</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.215624642035802</v>
+        <v>4.437499623195581</v>
       </c>
       <c r="C9" t="n">
-        <v>45.5953086283346</v>
+        <v>42.93280885441725</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.28906009787183</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>29.18245050873644</v>
+        <v>29.75186417719959</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>29.31989518733098</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.04572553593887</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.42257778564941</v>
       </c>
     </row>
     <row r="13">
@@ -2181,7 +2181,7 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
         <v>25.49598787928967</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2265,7 +2265,7 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>62.58837964114266</v>
+        <v>63.79200232654924</v>
       </c>
       <c r="D19" t="n">
         <v>5.416302084329653</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.965859814529614</v>
+        <v>4.713370728088937</v>
       </c>
       <c r="C2" t="n">
-        <v>6.009277697694727</v>
+        <v>4.340306600475149</v>
       </c>
       <c r="D2" t="n">
-        <v>26.62205249606076</v>
+        <v>20.70113209174824</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.65258448588365</v>
+        <v>18.41758693167016</v>
       </c>
       <c r="C3" t="n">
-        <v>22.97289627937536</v>
+        <v>25.37817815478005</v>
       </c>
       <c r="D3" t="n">
-        <v>93.09913479372503</v>
+        <v>97.67407909551517</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.62227348023901</v>
+        <v>37.26714285320892</v>
       </c>
       <c r="C4" t="n">
-        <v>110.7421227867444</v>
+        <v>106.2879334525767</v>
       </c>
       <c r="D4" t="n">
-        <v>158.7299505703286</v>
+        <v>174.7982152457361</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.11573272257667</v>
+        <v>39.07355862902306</v>
       </c>
       <c r="C5" t="n">
-        <v>214.9536598448392</v>
+        <v>165.5962940138308</v>
       </c>
       <c r="D5" t="n">
-        <v>117.8833555874358</v>
+        <v>136.0211444233956</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.57617239586842</v>
+        <v>38.52083467153211</v>
       </c>
       <c r="C6" t="n">
-        <v>227.2608490652772</v>
+        <v>159.7588221643792</v>
       </c>
       <c r="D6" t="n">
-        <v>54.98376192404687</v>
+        <v>64.92592092495433</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.2360046641135</v>
+        <v>26.35010838198439</v>
       </c>
       <c r="C7" t="n">
-        <v>187.8642954415569</v>
+        <v>142.7097915324291</v>
       </c>
       <c r="D7" t="n">
-        <v>34.49468733641593</v>
+        <v>37.30935800449154</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>12.2669375645639</v>
       </c>
       <c r="C8" t="n">
-        <v>132.5997536740954</v>
+        <v>109.4010554227433</v>
       </c>
       <c r="D8" t="n">
-        <v>29.04009709162065</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>73.66249374504666</v>
+        <v>66.11874438561416</v>
       </c>
       <c r="D9" t="n">
-        <v>28.84374755077128</v>
+        <v>29.28749751309084</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>2.562361508084175</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>39.43189654107314</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>30.03657101143117</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.21141991377833</v>
+        <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>15.40853021815369</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
         <v>14.87936820556466</v>
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2576,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>34.3032465340878</v>
       </c>
       <c r="D19" t="n">
         <v>3.610868056219768</v>
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.790707812546182</v>
+        <v>2.810743677258618</v>
       </c>
       <c r="C2" t="n">
-        <v>2.969786805346601</v>
+        <v>2.02534551386117</v>
       </c>
       <c r="D2" t="n">
-        <v>18.54128714240526</v>
+        <v>14.46212543125976</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.31388152791849</v>
+        <v>18.9280957378785</v>
       </c>
       <c r="C3" t="n">
-        <v>24.36697801940583</v>
+        <v>23.37050409959532</v>
       </c>
       <c r="D3" t="n">
-        <v>96.06401286055041</v>
+        <v>96.08855655315656</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.40454647407447</v>
+        <v>40.99385713852982</v>
       </c>
       <c r="C4" t="n">
-        <v>104.4501017502267</v>
+        <v>102.1400494021339</v>
       </c>
       <c r="D4" t="n">
-        <v>169.0932793363579</v>
+        <v>185.3912729745592</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.88287859022093</v>
+        <v>40.66889864842413</v>
       </c>
       <c r="C5" t="n">
-        <v>249.8547907308133</v>
+        <v>197.9448808687632</v>
       </c>
       <c r="D5" t="n">
-        <v>120.7058802371454</v>
+        <v>143.2124463570035</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.81389420901639</v>
+        <v>32.00006641992479</v>
       </c>
       <c r="C6" t="n">
-        <v>258.3351274000972</v>
+        <v>191.1953654020664</v>
       </c>
       <c r="D6" t="n">
-        <v>53.09193409796327</v>
+        <v>62.75233150775189</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.186393195086651</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>185.828150702949</v>
+        <v>146.7820810096449</v>
       </c>
       <c r="D7" t="n">
-        <v>34.31502750653876</v>
+        <v>36.65060529494193</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.67173641388307</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>91.96030745679872</v>
+        <v>81.94648087348126</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>31.46010518258904</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>30.06405994715006</v>
       </c>
       <c r="D9" t="n">
-        <v>30.84062238120929</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.33890824661018</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>23.63066724122073</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.19120412261664</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>22.92282714645877</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.75370449942107</v>
+        <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.26832022289564</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>12.90605532002857</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
         <v>12.541826921753</v>
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>29.42788743479814</v>
       </c>
       <c r="D18" t="n">
         <v>2.675262494072558</v>
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.805434028109884</v>
+        <v>3.268238107437631</v>
       </c>
       <c r="C2" t="n">
-        <v>8.19366633964388</v>
+        <v>5.136503988619312</v>
       </c>
       <c r="D2" t="n">
-        <v>14.06451761103981</v>
+        <v>14.26381239500191</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.47524800431347</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="C3" t="n">
-        <v>18.09851892778995</v>
+        <v>15.49197877301467</v>
       </c>
       <c r="D3" t="n">
-        <v>89.32922360941728</v>
+        <v>87.31664081571131</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.94134148411922</v>
+        <v>39.05392367493812</v>
       </c>
       <c r="C4" t="n">
-        <v>84.73169911042947</v>
+        <v>81.52825635147212</v>
       </c>
       <c r="D4" t="n">
-        <v>176.3425043845163</v>
+        <v>189.6412587862436</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.25794727097221</v>
+        <v>49.43099690882691</v>
       </c>
       <c r="C5" t="n">
-        <v>226.3419332141022</v>
+        <v>195.0487251412351</v>
       </c>
       <c r="D5" t="n">
-        <v>147.6303110261141</v>
+        <v>169.5723722160303</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.58246379272141</v>
+        <v>40.97618567985338</v>
       </c>
       <c r="C6" t="n">
-        <v>318.2295913407867</v>
+        <v>246.4206372613579</v>
       </c>
       <c r="D6" t="n">
-        <v>70.48064943558278</v>
+        <v>85.05174886201394</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.85187926984575</v>
+        <v>17.30723027816702</v>
       </c>
       <c r="C7" t="n">
-        <v>261.464939081236</v>
+        <v>203.5545872508294</v>
       </c>
       <c r="D7" t="n">
-        <v>39.16584291322225</v>
+        <v>43.83699849002857</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>5.340707511102648</v>
       </c>
       <c r="C8" t="n">
-        <v>150.9584357435108</v>
+        <v>126.7583548338269</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>33.54631905411351</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>2.218749811597791</v>
       </c>
       <c r="C9" t="n">
-        <v>59.68436993198057</v>
+        <v>55.57968278052466</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>24.20008090968388</v>
+        <v>24.91184799526281</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.21204180858408</v>
+        <v>23.63361248433346</v>
       </c>
       <c r="D11" t="n">
         <v>23.81130881880213</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>17.7912318963607</v>
       </c>
       <c r="D12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.47965802121596</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.44249047717483</v>
       </c>
     </row>
     <row r="15">
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
         <v>11.82515109765283</v>
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3170,7 +3170,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>33.52766584773283</v>
       </c>
       <c r="D17" t="n">
         <v>4.249985811684442</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.290998231084556</v>
+        <v>2.216786316189298</v>
       </c>
       <c r="C2" t="n">
-        <v>4.448298847942298</v>
+        <v>2.905973204570559</v>
       </c>
       <c r="D2" t="n">
-        <v>10.13556329864407</v>
+        <v>11.16639838810322</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.806276907093888</v>
+        <v>13.12105806725862</v>
       </c>
       <c r="C3" t="n">
-        <v>24.18535469412017</v>
+        <v>17.66164119940012</v>
       </c>
       <c r="D3" t="n">
-        <v>82.48153337229577</v>
+        <v>81.48505945248526</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.90381408717959</v>
+        <v>35.46759931132452</v>
       </c>
       <c r="C4" t="n">
-        <v>70.93519862264904</v>
+        <v>65.53656799699583</v>
       </c>
       <c r="D4" t="n">
-        <v>179.6480489047154</v>
+        <v>190.3559711149353</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>43.73686022419541</v>
+        <v>54.26610435224246</v>
       </c>
       <c r="C5" t="n">
-        <v>206.8296975921968</v>
+        <v>184.8876364022806</v>
       </c>
       <c r="D5" t="n">
-        <v>166.1853426363789</v>
+        <v>186.6302385773187</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.65417243286043</v>
+        <v>47.69821221083129</v>
       </c>
       <c r="C6" t="n">
-        <v>347.0095252907819</v>
+        <v>278.7024652724016</v>
       </c>
       <c r="D6" t="n">
-        <v>84.20646408865744</v>
+        <v>103.2052456612417</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.1750541909922</v>
+        <v>15.63040519931347</v>
       </c>
       <c r="C7" t="n">
-        <v>327.0407769864017</v>
+        <v>255.7757111351257</v>
       </c>
       <c r="D7" t="n">
-        <v>43.77711188006952</v>
+        <v>49.40645321622073</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>196.5213466976053</v>
+        <v>162.9750276434918</v>
       </c>
       <c r="D8" t="n">
-        <v>33.96356182841841</v>
+        <v>34.63115026730623</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>65.78593191387449</v>
+        <v>63.34530712111692</v>
       </c>
       <c r="D9" t="n">
-        <v>31.61718481526852</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.32127784566274</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.0343454741154</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.18701508989241</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3467,7 +3467,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
         <v>3.306526267903257</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.795616551067416</v>
+        <v>3.363467634749572</v>
       </c>
       <c r="C2" t="n">
-        <v>15.55481062608646</v>
+        <v>4.920519493685013</v>
       </c>
       <c r="D2" t="n">
-        <v>13.21137885604933</v>
+        <v>12.79609957715293</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>6.75933294373929</v>
+        <v>10.45561305022853</v>
       </c>
       <c r="C3" t="n">
-        <v>20.93576979306323</v>
+        <v>14.60840583919254</v>
       </c>
       <c r="D3" t="n">
-        <v>73.76852249710534</v>
+        <v>73.18929135159971</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.20713307006285</v>
+        <v>30.41356212986194</v>
       </c>
       <c r="C4" t="n">
-        <v>66.20022944506667</v>
+        <v>55.87518883950297</v>
       </c>
       <c r="D4" t="n">
-        <v>178.8567602550924</v>
+        <v>187.6630371621863</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.77965621255477</v>
+        <v>53.75068680751288</v>
       </c>
       <c r="C5" t="n">
-        <v>175.4874021341174</v>
+        <v>157.3005259129452</v>
       </c>
       <c r="D5" t="n">
-        <v>181.8933059043278</v>
+        <v>205.0625517245526</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.01393406097126</v>
+        <v>57.19760299712343</v>
       </c>
       <c r="C6" t="n">
-        <v>341.3742934684052</v>
+        <v>285.7465050503724</v>
       </c>
       <c r="D6" t="n">
-        <v>106.6266364105418</v>
+        <v>127.1952325622168</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.89475737366311</v>
+        <v>29.16477905005999</v>
       </c>
       <c r="C7" t="n">
-        <v>393.6346872608714</v>
+        <v>317.3391461730347</v>
       </c>
       <c r="D7" t="n">
-        <v>52.87987659384594</v>
+        <v>61.14422876819559</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.67588438887831</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>284.7264691856599</v>
+        <v>229.233180203109</v>
       </c>
       <c r="D8" t="n">
-        <v>36.46701847424777</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>125.6921768270148</v>
+        <v>113.489052863227</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.7117670855789376</v>
       </c>
       <c r="C10" t="n">
-        <v>45.41074005993622</v>
+        <v>45.98015372839937</v>
       </c>
       <c r="D10" t="n">
-        <v>26.05067533218912</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.9436648324262</v>
+        <v>27.72062817711293</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.39482680802324</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>16.65044106402591</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>11.67690719431156</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.36962016288231</v>
-      </c>
-      <c r="D14" t="n">
-        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.117449871611123</v>
+        <v>5.066799901617789</v>
       </c>
       <c r="C2" t="n">
-        <v>8.567712214961913</v>
+        <v>6.239988408192727</v>
       </c>
       <c r="D2" t="n">
-        <v>8.092546326106458</v>
+        <v>17.94242104281471</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.311614932873739</v>
+        <v>2.405281875404686</v>
       </c>
       <c r="C2" t="n">
-        <v>9.207811718130834</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="D2" t="n">
-        <v>9.830239762623313</v>
+        <v>9.418887474543899</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.311876974780997</v>
+        <v>14.17152811080271</v>
       </c>
       <c r="C3" t="n">
-        <v>34.91094836301658</v>
+        <v>18.12797135891735</v>
       </c>
       <c r="D3" t="n">
-        <v>79.79645340118076</v>
+        <v>79.20249604011144</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.68983414538279</v>
+        <v>41.36397602303086</v>
       </c>
       <c r="C4" t="n">
-        <v>97.74967366874218</v>
+        <v>83.18740997164923</v>
       </c>
       <c r="D4" t="n">
-        <v>180.6563037969768</v>
+        <v>193.1254813886156</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.87534340375644</v>
+        <v>33.20761609614836</v>
       </c>
       <c r="C5" t="n">
-        <v>276.7546778271759</v>
+        <v>237.7547502759714</v>
       </c>
       <c r="D5" t="n">
-        <v>163.4364490644878</v>
+        <v>185.6239471804657</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.81260936167588</v>
+        <v>18.07299348747954</v>
       </c>
       <c r="C6" t="n">
-        <v>319.4773926728844</v>
+        <v>265.016902275201</v>
       </c>
       <c r="D6" t="n">
-        <v>81.8316163920844</v>
+        <v>97.32850390362032</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.371722527011046</v>
+        <v>5.389794896314989</v>
       </c>
       <c r="C7" t="n">
-        <v>200.2009370931223</v>
+        <v>161.2147540097772</v>
       </c>
       <c r="D7" t="n">
-        <v>31.85967649821749</v>
+        <v>34.37491411649782</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>92.62789589568656</v>
+        <v>83.61545197070083</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>24.53387512912779</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.4437499623195582</v>
       </c>
       <c r="C9" t="n">
-        <v>34.61249706092553</v>
+        <v>35.05624702324509</v>
       </c>
       <c r="D9" t="n">
-        <v>19.85781081380023</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.35653864755762</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="D10" t="n">
-        <v>18.79065105928395</v>
+        <v>19.21771131063132</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>15.81497376771187</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.34806277111788</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.4519070435898</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>9.626036240139976</v>
+      </c>
+      <c r="D13" t="n">
         <v>9.365873098514571</v>
-      </c>
-      <c r="D13" t="n">
-        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.063674732055801</v>
+        <v>6.107452468119408</v>
       </c>
       <c r="C2" t="n">
-        <v>7.152032025438014</v>
+        <v>5.05698242457532</v>
       </c>
       <c r="D2" t="n">
-        <v>28.82902133520759</v>
+        <v>32.54689989119026</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.752280783360314</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C3" t="n">
-        <v>21.58863201638736</v>
+        <v>15.72268948351267</v>
       </c>
       <c r="D3" t="n">
-        <v>9.935286766977722</v>
+        <v>18.2065111752571</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.449321653375552</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>18.27425176685013</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39843513116856</v>
+        <v>13.39698199264245</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14474862788245</v>
+        <v>70.1371410203046</v>
       </c>
       <c r="D21" t="n">
-        <v>1.57628648601983</v>
+        <v>1.576115528546171</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.385466994870503</v>
+        <v>4.666246838285089</v>
       </c>
       <c r="C2" t="n">
-        <v>4.671155576806324</v>
+        <v>4.956844158742146</v>
       </c>
       <c r="D2" t="n">
-        <v>22.91202792171206</v>
+        <v>27.76087983298706</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.05924901962008</v>
+        <v>16.94987411382118</v>
       </c>
       <c r="C3" t="n">
-        <v>25.53034904893831</v>
+        <v>18.2212373908208</v>
       </c>
       <c r="D3" t="n">
-        <v>31.74972075534185</v>
+        <v>41.14504628498383</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.3250406055637</v>
+        <v>12.59680479319082</v>
       </c>
       <c r="C4" t="n">
-        <v>33.43832680664636</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D4" t="n">
-        <v>20.27996232662636</v>
+        <v>24.60652445924206</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.522330836388309</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.42267559664065</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.07441720354028</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.36098972218912</v>
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43885238644461</v>
+        <v>15.43628944709232</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13254489279623</v>
+        <v>86.11824638904137</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250284712935707</v>
+        <v>3.249745146756279</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.133558745506572</v>
+        <v>6.072109550766522</v>
       </c>
       <c r="C2" t="n">
-        <v>9.72028401974767</v>
+        <v>7.138287557578558</v>
       </c>
       <c r="D2" t="n">
-        <v>25.95544580487717</v>
+        <v>22.36813969355933</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.43936530761284</v>
+        <v>16.50808764691012</v>
       </c>
       <c r="C3" t="n">
-        <v>21.31374265919825</v>
+        <v>18.84464718301752</v>
       </c>
       <c r="D3" t="n">
-        <v>42.71093387325749</v>
+        <v>53.80468293124645</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.26193101505142</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="C4" t="n">
-        <v>50.75733805726435</v>
+        <v>36.4886169237412</v>
       </c>
       <c r="D4" t="n">
-        <v>31.61325782445154</v>
+        <v>39.66653424238812</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.449321653375552</v>
+        <v>11.21646752101981</v>
       </c>
       <c r="C5" t="n">
-        <v>37.52730599483434</v>
+        <v>28.17615911188346</v>
       </c>
       <c r="D5" t="n">
-        <v>29.96784867213389</v>
+        <v>31.48955761371645</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.27675504160637</v>
+        <v>12.3572583533546</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
-        <v>24.19419042345839</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5238,7 +5238,7 @@
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5347,7 +5347,7 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72915241538278</v>
+        <v>16.72571159091772</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0478297338349</v>
+        <v>102.0268407045981</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182288103845694</v>
+        <v>4.181427897729431</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.324017800130453</v>
+        <v>5.3711416899343</v>
       </c>
       <c r="C2" t="n">
-        <v>13.80140922630166</v>
+        <v>6.779949645528473</v>
       </c>
       <c r="D2" t="n">
-        <v>25.68153819539231</v>
+        <v>30.10823859384118</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.00877897607599</v>
+        <v>18.76610736667778</v>
       </c>
       <c r="C3" t="n">
-        <v>30.77288178961627</v>
+        <v>23.94973524510094</v>
       </c>
       <c r="D3" t="n">
-        <v>52.93583621298801</v>
+        <v>58.83613991551135</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.1162725019244</v>
+        <v>28.10350978176919</v>
       </c>
       <c r="C4" t="n">
-        <v>52.19952543480291</v>
+        <v>42.44880723622359</v>
       </c>
       <c r="D4" t="n">
-        <v>45.12897846881738</v>
+        <v>56.73029108990194</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.85017781634452</v>
+        <v>23.66011967234813</v>
       </c>
       <c r="C5" t="n">
-        <v>67.88785374866696</v>
+        <v>49.3573658310084</v>
       </c>
       <c r="D5" t="n">
-        <v>34.09118902997049</v>
+        <v>37.9690924617454</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.338384162795663</v>
+        <v>10.465430527271</v>
       </c>
       <c r="C6" t="n">
-        <v>36.58875518957439</v>
+        <v>28.98119222936585</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>38.64158963915446</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>8.623671834103982</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>39.52516257297658</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.84831213192725</v>
       </c>
       <c r="C8" t="n">
-        <v>31.62700229231099</v>
+        <v>31.37665662772806</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>39.8884092235479</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.6499990956694</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5619,7 +5619,7 @@
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04925915946834</v>
+        <v>18.04741639277205</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7499288022458</v>
+        <v>117.7379069433224</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016419719822779</v>
+        <v>6.015805464257349</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.993168823799278</v>
+        <v>5.431028299893355</v>
       </c>
       <c r="C2" t="n">
-        <v>11.60523961190155</v>
+        <v>8.006152528132739</v>
       </c>
       <c r="D2" t="n">
-        <v>37.6107545496953</v>
+        <v>41.3688847615521</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.86995163914969</v>
+        <v>16.51299638543135</v>
       </c>
       <c r="C3" t="n">
-        <v>40.92906179004953</v>
+        <v>23.78283813537898</v>
       </c>
       <c r="D3" t="n">
-        <v>57.08862900195202</v>
+        <v>64.56954650831271</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.14331946928681</v>
+        <v>23.82799852977434</v>
       </c>
       <c r="C4" t="n">
-        <v>54.62444226429253</v>
+        <v>43.71231653158923</v>
       </c>
       <c r="D4" t="n">
-        <v>52.90147504333937</v>
+        <v>63.27756652952392</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.78221624057323</v>
+        <v>20.0521968592411</v>
       </c>
       <c r="C5" t="n">
-        <v>61.8255616749429</v>
+        <v>48.25289966373074</v>
       </c>
       <c r="D5" t="n">
-        <v>33.87029579651497</v>
+        <v>39.46625771072178</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.98870205363455</v>
+        <v>11.55222523587222</v>
       </c>
       <c r="C6" t="n">
-        <v>49.50953672516665</v>
+        <v>36.58875518957439</v>
       </c>
       <c r="D6" t="n">
-        <v>31.23528495831652</v>
+        <v>32.48308629041422</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>5.329908286355933</v>
       </c>
       <c r="C7" t="n">
-        <v>23.53543771390878</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>30.84160412891355</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.74374815365835</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.39687241888974</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5941,10 +5941,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051197722815141</v>
+        <v>7.051971739508051</v>
       </c>
       <c r="C21" t="n">
-        <v>66.10497865139195</v>
+        <v>66.11223505788797</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406998576759463</v>
+        <v>4.407482337192532</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.693735774004001</v>
+        <v>4.451244091055038</v>
       </c>
       <c r="C2" t="n">
-        <v>12.17956201888593</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="D2" t="n">
-        <v>38.02014334236623</v>
+        <v>36.96476456030091</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.87133429748144</v>
+        <v>18.04943154257761</v>
       </c>
       <c r="C3" t="n">
-        <v>43.707407793068</v>
+        <v>28.62285431731576</v>
       </c>
       <c r="D3" t="n">
-        <v>74.8877148799467</v>
+        <v>83.71853547964676</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.70786545695773</v>
+        <v>28.95861203216817</v>
       </c>
       <c r="C4" t="n">
-        <v>84.31052934530759</v>
+        <v>53.75657729373835</v>
       </c>
       <c r="D4" t="n">
-        <v>70.53955429783758</v>
+        <v>81.82179891504191</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.63619787454772</v>
+        <v>29.35425635697964</v>
       </c>
       <c r="C5" t="n">
-        <v>85.41205026947252</v>
+        <v>68.20692175254716</v>
       </c>
       <c r="D5" t="n">
-        <v>45.52854978444584</v>
+        <v>54.83060928218437</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.76356303419254</v>
+        <v>20.52834449580081</v>
       </c>
       <c r="C6" t="n">
-        <v>77.76619914879835</v>
+        <v>60.21647718768238</v>
       </c>
       <c r="D6" t="n">
-        <v>35.42145716922493</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>10.12083708308037</v>
       </c>
       <c r="C7" t="n">
-        <v>50.783845245279</v>
+        <v>39.40538935305847</v>
       </c>
       <c r="D7" t="n">
-        <v>33.35684174719388</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="C8" t="n">
-        <v>26.28629478120835</v>
+        <v>23.78283813537898</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.34243432679967</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.59540643932586</v>
       </c>
     </row>
     <row r="11">
@@ -6193,10 +6193,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.909319358310797</v>
+        <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6294,7 +6294,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.267879287466918</v>
+        <v>7.27125643127029</v>
       </c>
       <c r="C21" t="n">
-        <v>75.40424760746927</v>
+        <v>75.43928547442925</v>
       </c>
       <c r="D21" t="n">
-        <v>5.450909465600188</v>
+        <v>5.453442323452717</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.232895190084747</v>
+        <v>5.242532740677968</v>
       </c>
       <c r="C2" t="n">
-        <v>9.051713833155592</v>
+        <v>7.533931882390022</v>
       </c>
       <c r="D2" t="n">
-        <v>33.69063596663779</v>
+        <v>28.43337701039612</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.43936530761284</v>
+        <v>16.54244881655876</v>
       </c>
       <c r="C3" t="n">
-        <v>45.80834788015617</v>
+        <v>24.89712177969911</v>
       </c>
       <c r="D3" t="n">
-        <v>87.12520001338319</v>
+        <v>93.86489800303754</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.31146036862027</v>
+        <v>32.26415655236718</v>
       </c>
       <c r="C4" t="n">
-        <v>98.60477591914113</v>
+        <v>64.13266877992288</v>
       </c>
       <c r="D4" t="n">
-        <v>90.36005869887643</v>
+        <v>105.4073057618673</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.17111150464198</v>
+        <v>37.20823799095412</v>
       </c>
       <c r="C5" t="n">
-        <v>124.1419972020092</v>
+        <v>85.01935118777379</v>
       </c>
       <c r="D5" t="n">
-        <v>60.57383335202821</v>
+        <v>71.83938825826036</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.82018560586937</v>
+        <v>30.63151012020474</v>
       </c>
       <c r="C6" t="n">
-        <v>107.8341860867654</v>
+        <v>86.78257006460107</v>
       </c>
       <c r="D6" t="n">
-        <v>41.70071548558752</v>
+        <v>46.20890094348888</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.88802400845363</v>
+        <v>17.78632315783946</v>
       </c>
       <c r="C7" t="n">
-        <v>83.8412539426776</v>
+        <v>65.39617807528853</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>37.24947139453248</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.011061266653972</v>
+        <v>8.511752595819845</v>
       </c>
       <c r="C8" t="n">
-        <v>48.06636759992384</v>
+        <v>39.30426933952106</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>28.51093507903161</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>33.88011327355743</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
         <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>24.73415166079414</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>31.47974013667398</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6566,7 +6566,7 @@
         <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.468681007003165</v>
+        <v>7.477496284224421</v>
       </c>
       <c r="C21" t="n">
-        <v>84.0226613287856</v>
+        <v>84.12183319752474</v>
       </c>
       <c r="D21" t="n">
-        <v>6.535095881127769</v>
+        <v>6.542809248696368</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_71_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_71_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497637740282</v>
+        <v>10.84497645667621</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890720993652</v>
+        <v>37.78907237559152</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.097234080449439</v>
+        <v>1.242892593576462</v>
       </c>
       <c r="C2" t="n">
-        <v>8.089601082993719</v>
+        <v>4.195989687950868</v>
       </c>
       <c r="D2" t="n">
-        <v>25.26429542108742</v>
+        <v>14.11851373477338</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.18549356284042</v>
+        <v>10.0187353218387</v>
       </c>
       <c r="C3" t="n">
-        <v>27.26313374693393</v>
+        <v>51.79210013754048</v>
       </c>
       <c r="D3" t="n">
-        <v>94.36068059368218</v>
+        <v>68.24619166071703</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.1492920709703</v>
+        <v>15.74919667152733</v>
       </c>
       <c r="C4" t="n">
-        <v>63.09888844735099</v>
+        <v>155.9476775764931</v>
       </c>
       <c r="D4" t="n">
-        <v>125.1384711218197</v>
+        <v>79.51174656694917</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.65693774952392</v>
+        <v>14.84893402673301</v>
       </c>
       <c r="C5" t="n">
-        <v>102.3717418603362</v>
+        <v>189.992724464364</v>
       </c>
       <c r="D5" t="n">
-        <v>92.25974050659401</v>
+        <v>47.0502587260284</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.65417243286043</v>
+        <v>10.22392059202629</v>
       </c>
       <c r="C6" t="n">
-        <v>110.2895370950867</v>
+        <v>129.7713385381604</v>
       </c>
       <c r="D6" t="n">
-        <v>56.79508643838223</v>
+        <v>28.90068891761761</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.82920126165683</v>
+        <v>5.749114556069321</v>
       </c>
       <c r="C7" t="n">
-        <v>95.93834915440679</v>
+        <v>61.08434215823654</v>
       </c>
       <c r="D7" t="n">
-        <v>42.10028680121597</v>
+        <v>29.04500583014188</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.76901155206151</v>
+        <v>5.9248473951295</v>
       </c>
       <c r="C8" t="n">
-        <v>62.75331325545612</v>
+        <v>30.79251674370121</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.21093688769282</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>38.2734342500619</v>
+        <v>29.50937249425062</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.27968458918587</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="C10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.46715734296802</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.96909246174538</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.49598787928967</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>35.38218726105505</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>19.66637001147211</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.23610247510475</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>83.65177663575797</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.669711798276759</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.9952555541057</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.669711798276759</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.263550353094651</v>
+        <v>1.449059611468292</v>
       </c>
       <c r="C2" t="n">
-        <v>10.81002397146163</v>
+        <v>11.33722248864217</v>
       </c>
       <c r="D2" t="n">
-        <v>37.48018210503048</v>
+        <v>19.05964993024758</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.99405276051229</v>
+        <v>7.048948516492098</v>
       </c>
       <c r="C3" t="n">
-        <v>29.20208546282137</v>
+        <v>32.42712667127215</v>
       </c>
       <c r="D3" t="n">
-        <v>92.36282401553993</v>
+        <v>63.88723185386118</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.03442758957343</v>
+        <v>17.58702837387736</v>
       </c>
       <c r="C4" t="n">
-        <v>64.83461838845936</v>
+        <v>143.3636355034575</v>
       </c>
       <c r="D4" t="n">
-        <v>140.9387186739679</v>
+        <v>94.01019666326607</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.50400609183966</v>
+        <v>18.94773069196344</v>
       </c>
       <c r="C5" t="n">
-        <v>108.973995171396</v>
+        <v>238.7855853654305</v>
       </c>
       <c r="D5" t="n">
-        <v>111.3547333541945</v>
+        <v>62.88094045700822</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>48.22148373719484</v>
+        <v>14.6516027381794</v>
       </c>
       <c r="C6" t="n">
-        <v>133.5549941903276</v>
+        <v>213.4947827563284</v>
       </c>
       <c r="D6" t="n">
-        <v>70.52090109145691</v>
+        <v>35.90447703971436</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.53083207502382</v>
+        <v>8.324238784308704</v>
       </c>
       <c r="C7" t="n">
-        <v>125.9415407438936</v>
+        <v>119.8331065280699</v>
       </c>
       <c r="D7" t="n">
-        <v>47.49008169753095</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.69524160552276</v>
+        <v>6.258641614573416</v>
       </c>
       <c r="C8" t="n">
-        <v>91.96030745679872</v>
+        <v>53.40707511102648</v>
       </c>
       <c r="D8" t="n">
-        <v>39.13737222979909</v>
+        <v>31.96079651175491</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.31718662392973</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>56.79999517690344</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>3.98589567924205</v>
       </c>
       <c r="C10" t="n">
-        <v>37.15424186722054</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>35.58835427894688</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>21.5935407549086</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>36.42283982755666</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>27.9631198600619</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.93362637120549</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>24.38563122578652</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.49242074137117</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>51.36503988619312</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.095892479846698</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>43.93222801734051</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.847197723517082</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0326706902824</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.828097438956718</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.496625469628643</v>
+        <v>0.8119053514121122</v>
       </c>
       <c r="C2" t="n">
-        <v>10.36725575684632</v>
+        <v>5.129631754689584</v>
       </c>
       <c r="D2" t="n">
-        <v>33.75935830593507</v>
+        <v>13.14952875068178</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.38813450054276</v>
+        <v>6.842781498600269</v>
       </c>
       <c r="C3" t="n">
-        <v>34.87658719336794</v>
+        <v>39.87368300798421</v>
       </c>
       <c r="D3" t="n">
-        <v>97.85570242080082</v>
+        <v>65.87036221643974</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.396291581813</v>
+        <v>19.05474119172634</v>
       </c>
       <c r="C4" t="n">
-        <v>68.26779011021046</v>
+        <v>135.1061555630376</v>
       </c>
       <c r="D4" t="n">
-        <v>149.579080219044</v>
+        <v>102.573981887411</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.2157731774186</v>
+        <v>18.70229376590174</v>
       </c>
       <c r="C5" t="n">
-        <v>112.1401315175919</v>
+        <v>279.1599597025806</v>
       </c>
       <c r="D5" t="n">
-        <v>130.9406000539184</v>
+        <v>69.65499961631122</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.53470231257858</v>
+        <v>11.23021198887927</v>
       </c>
       <c r="C6" t="n">
-        <v>149.2531399812341</v>
+        <v>251.6131008691193</v>
       </c>
       <c r="D6" t="n">
-        <v>83.96495415341272</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.15450390912779</v>
+        <v>4.132176087174825</v>
       </c>
       <c r="C7" t="n">
-        <v>155.1063197939536</v>
+        <v>106.5382791171596</v>
       </c>
       <c r="D7" t="n">
-        <v>54.85613472249477</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>28.70630287217673</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="C8" t="n">
-        <v>122.9197213102219</v>
+        <v>41.80772598535042</v>
       </c>
       <c r="D8" t="n">
-        <v>41.72427743048944</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.53281126596553</v>
+        <v>2.773437264497239</v>
       </c>
       <c r="C9" t="n">
-        <v>80.54061816099981</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>39.38280915586078</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>1.850594422505238</v>
       </c>
       <c r="C10" t="n">
-        <v>49.96604940764142</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>29.46715734296802</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.153193699591506</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>36.60544490054656</v>
+        <v>21.85664913964673</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>17.57426565372215</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>20.89551813718911</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>17.91689560250429</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.90573652485908</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>44.38874069981529</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>7.555530331883453</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>37.98872741583033</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.008434941058676</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109.1149260719244</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10.01054367632334</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.819219553698344</v>
+        <v>0.7156940763959247</v>
       </c>
       <c r="C2" t="n">
-        <v>7.132397071353077</v>
+        <v>6.902668108559324</v>
       </c>
       <c r="D2" t="n">
-        <v>27.9464301490897</v>
+        <v>11.51491882311084</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.87824758914017</v>
+        <v>4.859651136021712</v>
       </c>
       <c r="C3" t="n">
-        <v>50.1231290403209</v>
+        <v>29.59969328304133</v>
       </c>
       <c r="D3" t="n">
-        <v>106.9172337309989</v>
+        <v>61.4230451162017</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.19437034990764</v>
+        <v>16.4511462800638</v>
       </c>
       <c r="C4" t="n">
-        <v>93.33377249504001</v>
+        <v>118.5018566411112</v>
       </c>
       <c r="D4" t="n">
-        <v>144.7037211197544</v>
+        <v>110.6655464658132</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.13965452037709</v>
+        <v>22.97289627937537</v>
       </c>
       <c r="C5" t="n">
-        <v>89.16723523821656</v>
+        <v>267.3053561738004</v>
       </c>
       <c r="D5" t="n">
-        <v>85.36296288426017</v>
+        <v>87.79278845227103</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.01515248838698</v>
+        <v>16.62393387601124</v>
       </c>
       <c r="C6" t="n">
-        <v>102.1587026085146</v>
+        <v>338.8384391483357</v>
       </c>
       <c r="D6" t="n">
-        <v>36.10573531908495</v>
+        <v>46.16864928761476</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.98405535702057</v>
+        <v>7.126506585127596</v>
       </c>
       <c r="C7" t="n">
-        <v>86.41637817091699</v>
+        <v>216.1906619521901</v>
       </c>
       <c r="D7" t="n">
-        <v>29.34443887993716</v>
+        <v>35.2133266559246</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.09727513817844</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>59.33192250615598</v>
+        <v>81.27889243459342</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>38.05155926890212</v>
+        <v>35.61093447614454</v>
       </c>
       <c r="D9" t="n">
-        <v>27.29062268265283</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.701188845010476</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
         <v>28.61303684027329</v>
       </c>
       <c r="D10" t="n">
-        <v>28.32833000604172</v>
+        <v>31.17539834835747</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>25.05518316008284</v>
       </c>
       <c r="D11" t="n">
-        <v>28.96450251839364</v>
+        <v>31.62994753542373</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>23.15451960466103</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
+        <v>21.20280516861837</v>
+      </c>
+      <c r="D14" t="n">
         <v>20.58823110575986</v>
-      </c>
-      <c r="D14" t="n">
-        <v>24.27567548291088</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.27523351455437</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>38.02505208088746</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>45.33318199130072</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>0.5350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>73.30219233758808</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.019275101186442</v>
+        <v>0.5006913291658733</v>
       </c>
       <c r="C2" t="n">
-        <v>3.316343744945725</v>
+        <v>5.558655501445441</v>
       </c>
       <c r="D2" t="n">
-        <v>19.14506198051705</v>
+        <v>9.2490451217092</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.2085157283946</v>
+        <v>3.897538385859837</v>
       </c>
       <c r="C3" t="n">
-        <v>39.56934121966769</v>
+        <v>28.61794557879453</v>
       </c>
       <c r="D3" t="n">
-        <v>106.2447365535898</v>
+        <v>57.6187727622453</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.6560538128109</v>
+        <v>14.01346673041897</v>
       </c>
       <c r="C4" t="n">
-        <v>112.0183948022653</v>
+        <v>102.2932020439964</v>
       </c>
       <c r="D4" t="n">
-        <v>160.8740875564036</v>
+        <v>114.9538204379633</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.30579086657305</v>
+        <v>24.66641106920112</v>
       </c>
       <c r="C5" t="n">
-        <v>127.9953569411779</v>
+        <v>257.6105975943631</v>
       </c>
       <c r="D5" t="n">
-        <v>108.4585776266664</v>
+        <v>101.19364461524</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.20761609614837</v>
+        <v>20.20633124880786</v>
       </c>
       <c r="C6" t="n">
-        <v>122.204027233826</v>
+        <v>383.6787837921045</v>
       </c>
       <c r="D6" t="n">
-        <v>46.69192081397831</v>
+        <v>54.94351026817275</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.66654993792135</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>111.329207913884</v>
+        <v>301.4691945338851</v>
       </c>
       <c r="D7" t="n">
-        <v>32.63820242768521</v>
+        <v>38.92629647338602</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>77.52370746584938</v>
+        <v>125.0059351817464</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>42.93280885441725</v>
+        <v>42.15624642035802</v>
       </c>
       <c r="D9" t="n">
-        <v>28.28906009787183</v>
+        <v>39.93749660876023</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>31.17539834835747</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>29.75186417719959</v>
+        <v>32.17187226816798</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.51842920776709</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.04572553593887</v>
+        <v>21.26269177857742</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>23.67484588791184</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.28621266575034</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>32.25041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>38.85168364786328</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.79200232654924</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.713370728088937</v>
+        <v>0.6597344572538566</v>
       </c>
       <c r="C2" t="n">
-        <v>4.340306600475149</v>
+        <v>11.55909746980195</v>
       </c>
       <c r="D2" t="n">
-        <v>20.70113209174824</v>
+        <v>13.94965312964293</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.41758693167016</v>
+        <v>2.861794557879453</v>
       </c>
       <c r="C3" t="n">
-        <v>25.37817815478005</v>
+        <v>25.38799563182252</v>
       </c>
       <c r="D3" t="n">
-        <v>97.67407909551517</v>
+        <v>52.56277208537423</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.26714285320892</v>
+        <v>11.10356653503143</v>
       </c>
       <c r="C4" t="n">
-        <v>106.2879334525767</v>
+        <v>88.38183707481912</v>
       </c>
       <c r="D4" t="n">
-        <v>174.7982152457361</v>
+        <v>116.4725841364331</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.07355862902306</v>
+        <v>23.29196428325558</v>
       </c>
       <c r="C5" t="n">
-        <v>165.5962940138308</v>
+        <v>227.6918363074415</v>
       </c>
       <c r="D5" t="n">
-        <v>136.0211444233956</v>
+        <v>114.2263453891164</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.52083467153211</v>
+        <v>24.99627829782805</v>
       </c>
       <c r="C6" t="n">
-        <v>159.7588221643792</v>
+        <v>395.3517639955991</v>
       </c>
       <c r="D6" t="n">
-        <v>64.92592092495433</v>
+        <v>68.06555008313562</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.35010838198439</v>
+        <v>12.45641487148353</v>
       </c>
       <c r="C7" t="n">
-        <v>142.7097915324291</v>
+        <v>404.5939368833784</v>
       </c>
       <c r="D7" t="n">
-        <v>37.30935800449154</v>
+        <v>43.5375654402333</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.2669375645639</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>109.4010554227433</v>
+        <v>226.1455836732528</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>39.22082078466007</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>66.11874438561416</v>
+        <v>82.64843048201772</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>39.43189654107314</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>30.20837685967435</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2495,7 @@
         <v>19.25207248027995</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>16.59349969717959</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.40853021815369</v>
+        <v>34.04210164475815</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>9.675123625352315</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>36.78510473042374</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.810743677258618</v>
+        <v>0.4741841411512094</v>
       </c>
       <c r="C2" t="n">
-        <v>2.02534551386117</v>
+        <v>6.657231182497622</v>
       </c>
       <c r="D2" t="n">
-        <v>14.46212543125976</v>
+        <v>10.26711749101314</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.9280957378785</v>
+        <v>4.084070449666732</v>
       </c>
       <c r="C3" t="n">
-        <v>23.37050409959532</v>
+        <v>34.87658719336794</v>
       </c>
       <c r="D3" t="n">
-        <v>96.08855655315656</v>
+        <v>57.93293202760429</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.99385713852982</v>
+        <v>16.82126516456485</v>
       </c>
       <c r="C4" t="n">
-        <v>102.1400494021339</v>
+        <v>128.6865073249677</v>
       </c>
       <c r="D4" t="n">
-        <v>185.3912729745592</v>
+        <v>118.2338395178519</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.66889864842413</v>
+        <v>14.50532233024663</v>
       </c>
       <c r="C5" t="n">
-        <v>197.9448808687632</v>
+        <v>337.7948413387213</v>
       </c>
       <c r="D5" t="n">
-        <v>143.2124463570035</v>
+        <v>102.5680914011855</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.00006641992479</v>
+        <v>7.728317927830893</v>
       </c>
       <c r="C6" t="n">
-        <v>191.1953654020664</v>
+        <v>340.0862404804334</v>
       </c>
       <c r="D6" t="n">
-        <v>62.75233150775189</v>
+        <v>58.28439770572465</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.084692344472483</v>
+        <v>3.293763547748049</v>
       </c>
       <c r="C7" t="n">
-        <v>146.7820810096449</v>
+        <v>158.9989494412922</v>
       </c>
       <c r="D7" t="n">
-        <v>36.65060529494193</v>
+        <v>33.11729530735765</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>81.94648087348126</v>
+        <v>60.91744504851459</v>
       </c>
       <c r="D8" t="n">
-        <v>31.46010518258904</v>
+        <v>29.79113408536946</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>30.06405994715006</v>
+        <v>28.73281006019139</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>25.5156228333746</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>23.63066724122073</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>19.01350778814797</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2792,7 +2792,7 @@
         <v>15.62156946997525</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>13.52848336452105</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>12.90605532002857</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>7.989462817160544</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.268238107437631</v>
+        <v>0.2631083847381452</v>
       </c>
       <c r="C2" t="n">
-        <v>5.136503988619312</v>
+        <v>4.101741908343174</v>
       </c>
       <c r="D2" t="n">
-        <v>14.26381239500191</v>
+        <v>7.733226666352125</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.33351648200343</v>
+        <v>2.896155727528091</v>
       </c>
       <c r="C3" t="n">
-        <v>15.49197877301467</v>
+        <v>30.32618658418397</v>
       </c>
       <c r="D3" t="n">
-        <v>87.31664081571131</v>
+        <v>53.10273332270997</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.05392367493812</v>
+        <v>11.72893982263664</v>
       </c>
       <c r="C4" t="n">
-        <v>81.52825635147212</v>
+        <v>105.024424157211</v>
       </c>
       <c r="D4" t="n">
-        <v>189.6412587862436</v>
+        <v>114.5454133929966</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.43099690882691</v>
+        <v>14.70167187109599</v>
       </c>
       <c r="C5" t="n">
-        <v>195.0487251412351</v>
+        <v>262.2002681117169</v>
       </c>
       <c r="D5" t="n">
-        <v>169.5723722160303</v>
+        <v>105.3906160508951</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.97618567985338</v>
+        <v>7.567311304334416</v>
       </c>
       <c r="C6" t="n">
-        <v>246.4206372613579</v>
+        <v>347.9353133758867</v>
       </c>
       <c r="D6" t="n">
-        <v>85.05174886201394</v>
+        <v>61.02151030516475</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.30723027816702</v>
+        <v>2.515237618280328</v>
       </c>
       <c r="C7" t="n">
-        <v>203.5545872508294</v>
+        <v>206.0099382591507</v>
       </c>
       <c r="D7" t="n">
-        <v>43.83699849002857</v>
+        <v>31.4404702285041</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.340707511102648</v>
+        <v>1.001382658331746</v>
       </c>
       <c r="C8" t="n">
-        <v>126.7583548338269</v>
+        <v>71.8492057353028</v>
       </c>
       <c r="D8" t="n">
-        <v>33.54631905411351</v>
+        <v>25.53525778745954</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.218749811597791</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>55.57968278052466</v>
+        <v>26.73593522975338</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>19.96874830438012</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D10" t="n">
-        <v>24.91184799526281</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>12.26104707833841</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>16.8811517745239</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>11.0652783745658</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>7.804894248762142</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>14.74977750860408</v>
       </c>
       <c r="D14" t="n">
-        <v>14.44249047717483</v>
+        <v>2.458296251434013</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.52766584773283</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.216786316189298</v>
+        <v>0.4241150082346221</v>
       </c>
       <c r="C2" t="n">
-        <v>2.905973204570559</v>
+        <v>5.915029918087032</v>
       </c>
       <c r="D2" t="n">
-        <v>11.16639838810322</v>
+        <v>10.54397034361074</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.12105806725862</v>
+        <v>1.86532063806894</v>
       </c>
       <c r="C3" t="n">
-        <v>17.66164119940012</v>
+        <v>22.54092728950677</v>
       </c>
       <c r="D3" t="n">
-        <v>81.48505945248526</v>
+        <v>47.36932672990861</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.46759931132452</v>
+        <v>8.653124265231385</v>
       </c>
       <c r="C4" t="n">
-        <v>65.53656799699583</v>
+        <v>89.51771916863267</v>
       </c>
       <c r="D4" t="n">
-        <v>190.3559711149353</v>
+        <v>115.119735799981</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.26610435224246</v>
+        <v>16.29701189049706</v>
       </c>
       <c r="C5" t="n">
-        <v>184.8876364022806</v>
+        <v>227.2500498405305</v>
       </c>
       <c r="D5" t="n">
-        <v>186.6302385773187</v>
+        <v>120.9267734706009</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.69821221083129</v>
+        <v>12.92078153559227</v>
       </c>
       <c r="C6" t="n">
-        <v>278.7024652724016</v>
+        <v>386.3756447356705</v>
       </c>
       <c r="D6" t="n">
-        <v>103.2052456612417</v>
+        <v>77.36368259005717</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.63040519931347</v>
+        <v>5.270021676396877</v>
       </c>
       <c r="C7" t="n">
-        <v>255.7757111351257</v>
+        <v>346.3841520031766</v>
       </c>
       <c r="D7" t="n">
-        <v>49.40645321622073</v>
+        <v>39.82459562277186</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="C8" t="n">
-        <v>162.9750276434918</v>
+        <v>165.3115871795991</v>
       </c>
       <c r="D8" t="n">
-        <v>34.63115026730623</v>
+        <v>27.70492021384499</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>63.34530712111692</v>
+        <v>54.58124536530566</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>21.52187317249857</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>31.03304493124168</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.07183181332604</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>14.9264920953685</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.59193711239859</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>12.36707583039707</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>13.66887328622834</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.51878906066559</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.363467634749572</v>
+        <v>0.7422012644105886</v>
       </c>
       <c r="C2" t="n">
-        <v>4.920519493685013</v>
+        <v>10.90230825566083</v>
       </c>
       <c r="D2" t="n">
-        <v>12.79609957715293</v>
+        <v>9.910743074371551</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.45561305022853</v>
+        <v>1.629701189049706</v>
       </c>
       <c r="C3" t="n">
-        <v>14.60840583919254</v>
+        <v>22.60474089028281</v>
       </c>
       <c r="D3" t="n">
-        <v>73.18929135159971</v>
+        <v>44.94440990041898</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.41356212986194</v>
+        <v>6.215444715586556</v>
       </c>
       <c r="C4" t="n">
-        <v>55.87518883950297</v>
+        <v>73.41116633275949</v>
       </c>
       <c r="D4" t="n">
-        <v>187.6630371621863</v>
+        <v>111.7376149588507</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.75068680751288</v>
+        <v>15.0207398749762</v>
       </c>
       <c r="C5" t="n">
-        <v>157.3005259129452</v>
+        <v>198.1903177948249</v>
       </c>
       <c r="D5" t="n">
-        <v>205.0625517245526</v>
+        <v>132.6586585363503</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.19760299712343</v>
+        <v>16.62393387601124</v>
       </c>
       <c r="C6" t="n">
-        <v>285.7465050503724</v>
+        <v>373.2536049207076</v>
       </c>
       <c r="D6" t="n">
-        <v>127.1952325622168</v>
+        <v>93.7461065308237</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>29.16477905005999</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>317.3391461730347</v>
+        <v>442.5021609874606</v>
       </c>
       <c r="D7" t="n">
-        <v>61.14422876819559</v>
+        <v>49.34656660626167</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>3.254493639578176</v>
       </c>
       <c r="C8" t="n">
-        <v>229.233180203109</v>
+        <v>292.7375304523139</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>0.9984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>113.489052863227</v>
+        <v>117.5937400146829</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>23.18593553119691</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>45.98015372839937</v>
+        <v>39.57424995818893</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72062817711293</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.12502611580461</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>14.31977201414398</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>11.36962016288231</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>6.450082416901544</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.066799901617789</v>
+        <v>4.793874039837175</v>
       </c>
       <c r="C2" t="n">
-        <v>6.239988408192727</v>
+        <v>20.36733787230433</v>
       </c>
       <c r="D2" t="n">
-        <v>17.94242104281471</v>
+        <v>9.256899103343175</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.405281875404686</v>
+        <v>0.5978843518863075</v>
       </c>
       <c r="C2" t="n">
-        <v>2.833323874456295</v>
+        <v>23.53838295702153</v>
       </c>
       <c r="D2" t="n">
-        <v>9.418887474543899</v>
+        <v>11.70537787773472</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.17152811080271</v>
+        <v>1.938951715887451</v>
       </c>
       <c r="C3" t="n">
-        <v>18.12797135891735</v>
+        <v>31.33738671955819</v>
       </c>
       <c r="D3" t="n">
-        <v>79.20249604011144</v>
+        <v>43.04963683122264</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.36397602303086</v>
+        <v>4.747731897737575</v>
       </c>
       <c r="C4" t="n">
-        <v>83.18740997164923</v>
+        <v>65.26855087373644</v>
       </c>
       <c r="D4" t="n">
-        <v>193.1254813886156</v>
+        <v>107.9470870727538</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>33.20761609614836</v>
+        <v>12.73817646260237</v>
       </c>
       <c r="C5" t="n">
-        <v>237.7547502759714</v>
+        <v>169.7196343716674</v>
       </c>
       <c r="D5" t="n">
-        <v>185.6239471804657</v>
+        <v>139.6536109291088</v>
       </c>
     </row>
     <row r="6">
@@ -4260,10 +4260,10 @@
         <v>18.07299348747954</v>
       </c>
       <c r="C6" t="n">
-        <v>265.016902275201</v>
+        <v>351.5982140604315</v>
       </c>
       <c r="D6" t="n">
-        <v>97.32850390362032</v>
+        <v>107.0694046251572</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.389794896314989</v>
+        <v>13.1750541909922</v>
       </c>
       <c r="C7" t="n">
-        <v>161.2147540097772</v>
+        <v>479.9911788218293</v>
       </c>
       <c r="D7" t="n">
-        <v>34.37491411649782</v>
+        <v>60.30581622876881</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>83.61545197070083</v>
+        <v>409.9827500319893</v>
       </c>
       <c r="D8" t="n">
-        <v>24.53387512912779</v>
+        <v>34.96494448675015</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>35.05624702324509</v>
+        <v>209.4499822148314</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>25.07187287105504</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>21.6377194015997</v>
+        <v>76.58613840829368</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>21.06830573313655</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>28.60910984945629</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>13.4519070435898</v>
+        <v>14.75370449942107</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
         <v>9.365873098514571</v>
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.107452468119408</v>
+        <v>4.449280595646544</v>
       </c>
       <c r="C2" t="n">
-        <v>5.05698242457532</v>
+        <v>16.97932654494858</v>
       </c>
       <c r="D2" t="n">
-        <v>32.54689989119026</v>
+        <v>24.76556758733004</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.76486357706628</v>
+        <v>7.731263170943632</v>
       </c>
       <c r="C3" t="n">
-        <v>15.72268948351267</v>
+        <v>40.21238596594935</v>
       </c>
       <c r="D3" t="n">
-        <v>18.2065111752571</v>
+        <v>9.35114688295087</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.449321653375552</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.27425176685013</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39698199264245</v>
+        <v>11.67684011393173</v>
       </c>
       <c r="C21" t="n">
-        <v>70.1371410203046</v>
+        <v>59.94111258484956</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576115528546171</v>
+        <v>0.7784560075954489</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.666246838285089</v>
+        <v>2.270782439922872</v>
       </c>
       <c r="C2" t="n">
-        <v>4.956844158742146</v>
+        <v>9.681995859282043</v>
       </c>
       <c r="D2" t="n">
-        <v>27.76087983298706</v>
+        <v>25.69233742013903</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.94987411382118</v>
+        <v>12.5271007061893</v>
       </c>
       <c r="C3" t="n">
-        <v>18.2212373908208</v>
+        <v>57.36351835914113</v>
       </c>
       <c r="D3" t="n">
-        <v>41.14504628498383</v>
+        <v>28.79466016555895</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>12.59680479319082</v>
+        <v>9.457175635009525</v>
       </c>
       <c r="C4" t="n">
-        <v>24.5171854181556</v>
+        <v>64.86014382876978</v>
       </c>
       <c r="D4" t="n">
-        <v>24.60652445924206</v>
+        <v>19.11855479250239</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.429825568010856</v>
       </c>
       <c r="C5" t="n">
-        <v>5.522330836388309</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.07441720354028</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>6.989061906533041</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>44.84132639147307</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>25.05518316008284</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43628944709232</v>
+        <v>13.62153733865966</v>
       </c>
       <c r="C21" t="n">
-        <v>86.11824638904137</v>
+        <v>73.71655500921695</v>
       </c>
       <c r="D21" t="n">
-        <v>3.249745146756279</v>
+        <v>1.602533804548195</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.072109550766522</v>
+        <v>1.762237129123025</v>
       </c>
       <c r="C2" t="n">
-        <v>7.138287557578558</v>
+        <v>7.573201790559895</v>
       </c>
       <c r="D2" t="n">
-        <v>22.36813969355933</v>
+        <v>20.48023885829271</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.50808764691012</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C3" t="n">
-        <v>18.84464718301752</v>
+        <v>45.09658079457724</v>
       </c>
       <c r="D3" t="n">
-        <v>53.80468293124645</v>
+        <v>43.6926815775043</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.0832529328785</v>
+        <v>17.98267269868883</v>
       </c>
       <c r="C4" t="n">
-        <v>36.4886169237412</v>
+        <v>112.8607343325091</v>
       </c>
       <c r="D4" t="n">
-        <v>39.66653424238812</v>
+        <v>29.04795107325463</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>11.21646752101981</v>
+        <v>8.762098260402784</v>
       </c>
       <c r="C5" t="n">
-        <v>28.17615911188346</v>
+        <v>72.74750488468867</v>
       </c>
       <c r="D5" t="n">
-        <v>31.48955761371645</v>
+        <v>27.04714925199963</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.3572583533546</v>
+        <v>10.62643715076748</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>31.83905979642831</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.886960145291375</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>32.33876937788993</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>29.29044275620359</v>
+        <v>23.61594102565702</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.85156047467625</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>36.60937189136354</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>43.98720588877834</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.77947628610551</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.8744848292392</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72571159091772</v>
+        <v>14.81838481896472</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0268407045981</v>
+        <v>87.26382171168113</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181427897729431</v>
+        <v>2.469730803160787</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.3711416899343</v>
+        <v>2.398409641474958</v>
       </c>
       <c r="C2" t="n">
-        <v>6.779949645528473</v>
+        <v>6.853580723346982</v>
       </c>
       <c r="D2" t="n">
-        <v>30.10823859384118</v>
+        <v>25.90341317655209</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.76610736667778</v>
+        <v>7.809802987283376</v>
       </c>
       <c r="C3" t="n">
-        <v>23.94973524510094</v>
+        <v>35.87796985169969</v>
       </c>
       <c r="D3" t="n">
-        <v>58.83613991551135</v>
+        <v>49.53898915629405</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.10350978176919</v>
+        <v>18.64633414675967</v>
       </c>
       <c r="C4" t="n">
-        <v>42.44880723622359</v>
+        <v>112.9117852131299</v>
       </c>
       <c r="D4" t="n">
-        <v>56.73029108990194</v>
+        <v>43.30390948662256</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.66011967234813</v>
+        <v>18.06415775814131</v>
       </c>
       <c r="C5" t="n">
-        <v>49.3573658310084</v>
+        <v>147.4094177926586</v>
       </c>
       <c r="D5" t="n">
-        <v>37.9690924617454</v>
+        <v>31.46501392111028</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.465430527271</v>
+        <v>8.211337798320324</v>
       </c>
       <c r="C6" t="n">
-        <v>28.98119222936585</v>
+        <v>65.77120569831082</v>
       </c>
       <c r="D6" t="n">
-        <v>38.64158963915446</v>
+        <v>33.52962934314132</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>17.78632315783946</v>
       </c>
       <c r="D7" t="n">
-        <v>39.52516257297658</v>
+        <v>34.19525428662065</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.37665662772806</v>
+        <v>25.2849121228766</v>
       </c>
       <c r="D8" t="n">
-        <v>39.8884092235479</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>33.61405964570653</v>
+        <v>27.29062268265283</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.59540643932586</v>
+        <v>27.18950266911542</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>43.41779222031519</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.7623035490478</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.06370009425158</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.74234979979338</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.74489413227862</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04741639277205</v>
+        <v>16.03837199113534</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7379069433224</v>
+        <v>100.4508561550055</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015805464257349</v>
+        <v>3.376499366554808</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.431028299893355</v>
+        <v>2.715514149946678</v>
       </c>
       <c r="C2" t="n">
-        <v>8.006152528132739</v>
+        <v>13.52455637370406</v>
       </c>
       <c r="D2" t="n">
-        <v>41.3688847615521</v>
+        <v>22.47613194102647</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.51299638543135</v>
+        <v>7.947247665877931</v>
       </c>
       <c r="C3" t="n">
-        <v>23.78283813537898</v>
+        <v>30.71397692736146</v>
       </c>
       <c r="D3" t="n">
-        <v>64.56954650831271</v>
+        <v>57.64331645485147</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.82799852977434</v>
+        <v>16.82126516456485</v>
       </c>
       <c r="C4" t="n">
-        <v>43.71231653158923</v>
+        <v>100.5702348230433</v>
       </c>
       <c r="D4" t="n">
-        <v>63.27756652952392</v>
+        <v>56.75581653021235</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.0521968592411</v>
+        <v>22.67837196810132</v>
       </c>
       <c r="C5" t="n">
-        <v>48.25289966373074</v>
+        <v>178.4817326320702</v>
       </c>
       <c r="D5" t="n">
-        <v>39.46625771072178</v>
+        <v>38.65631585471817</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.55222523587222</v>
+        <v>15.81890075852886</v>
       </c>
       <c r="C6" t="n">
-        <v>36.58875518957439</v>
+        <v>147.200305531654</v>
       </c>
       <c r="D6" t="n">
-        <v>32.48308629041422</v>
+        <v>35.98498035146259</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.329908286355933</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>20.4213339960379</v>
+        <v>55.39511421212627</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>35.93196597543326</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.760715602071035</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>25.03456645829366</v>
       </c>
       <c r="D8" t="n">
-        <v>30.0414797499524</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.098436812331936</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>29.95312245657017</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.60624672180155</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>30.03657101143117</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>43.13308538608361</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.38607319414302</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>46.20104696185489</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>26.87534340375643</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051971739508051</v>
+        <v>17.27356292882991</v>
       </c>
       <c r="C21" t="n">
-        <v>66.11223505788797</v>
+        <v>113.1418371838359</v>
       </c>
       <c r="D21" t="n">
-        <v>4.407482337192532</v>
+        <v>4.318390732207478</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.451244091055038</v>
+        <v>2.677225989481052</v>
       </c>
       <c r="C2" t="n">
-        <v>5.757950285407543</v>
+        <v>15.18469174158542</v>
       </c>
       <c r="D2" t="n">
-        <v>36.96476456030091</v>
+        <v>25.81505588316988</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.04943154257761</v>
+        <v>8.511752595819846</v>
       </c>
       <c r="C3" t="n">
-        <v>28.62285431731576</v>
+        <v>41.54265410520378</v>
       </c>
       <c r="D3" t="n">
-        <v>83.71853547964676</v>
+        <v>61.21196935978863</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.95861203216817</v>
+        <v>15.77472211183775</v>
       </c>
       <c r="C4" t="n">
-        <v>53.75657729373835</v>
+        <v>88.72643051900974</v>
       </c>
       <c r="D4" t="n">
-        <v>81.82179891504191</v>
+        <v>70.22048629395735</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.35425635697964</v>
+        <v>23.73375075016664</v>
       </c>
       <c r="C5" t="n">
-        <v>68.20692175254716</v>
+        <v>181.5006068226291</v>
       </c>
       <c r="D5" t="n">
-        <v>54.83060928218437</v>
+        <v>48.30198704894308</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.52834449580081</v>
+        <v>22.37992066601029</v>
       </c>
       <c r="C6" t="n">
-        <v>60.21647718768238</v>
+        <v>207.2155244399658</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>39.08435785376978</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.12083708308037</v>
+        <v>12.6360747013607</v>
       </c>
       <c r="C7" t="n">
-        <v>39.40538935305847</v>
+        <v>125.8816541339345</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>38.14777054391831</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.591053175685585</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>23.78283813537898</v>
+        <v>46.2304993929823</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>38.21943812632832</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>24.34243432679967</v>
+        <v>32.88363935374691</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>42.99073196896783</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.292021036517808</v>
       </c>
       <c r="C12" t="n">
-        <v>22.34752299177014</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.00006641992479</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>30.42141611149592</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>42.40561033723673</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.30869505195678</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.27125643127029</v>
+        <v>17.6357354543427</v>
       </c>
       <c r="C21" t="n">
-        <v>75.43928547442925</v>
+        <v>125.2137217258332</v>
       </c>
       <c r="D21" t="n">
-        <v>5.453442323452717</v>
+        <v>5.290720636302809</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.242532740677968</v>
+        <v>2.474985962406209</v>
       </c>
       <c r="C2" t="n">
-        <v>7.533931882390022</v>
+        <v>9.960812207288139</v>
       </c>
       <c r="D2" t="n">
-        <v>28.43337701039612</v>
+        <v>20.79734336676443</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.54244881655876</v>
+        <v>10.75013736150257</v>
       </c>
       <c r="C3" t="n">
-        <v>24.89712177969911</v>
+        <v>63.91668428498858</v>
       </c>
       <c r="D3" t="n">
-        <v>93.86489800303754</v>
+        <v>66.0667117572891</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.26415655236718</v>
+        <v>11.39710909860122</v>
       </c>
       <c r="C4" t="n">
-        <v>64.13266877992288</v>
+        <v>141.7044818832804</v>
       </c>
       <c r="D4" t="n">
-        <v>105.4073057618673</v>
+        <v>63.62215997371455</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.20823799095412</v>
+        <v>12.59091430696535</v>
       </c>
       <c r="C5" t="n">
-        <v>85.01935118777379</v>
+        <v>123.822929198129</v>
       </c>
       <c r="D5" t="n">
-        <v>71.83938825826036</v>
+        <v>36.79099521664922</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.63151012020474</v>
+        <v>7.808821239579131</v>
       </c>
       <c r="C6" t="n">
-        <v>86.78257006460107</v>
+        <v>82.8781594448115</v>
       </c>
       <c r="D6" t="n">
-        <v>46.20890094348888</v>
+        <v>25.1170332654504</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.78632315783946</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>65.39617807528853</v>
+        <v>32.45854259780804</v>
       </c>
       <c r="D7" t="n">
-        <v>37.24947139453248</v>
+        <v>26.82920126165683</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.511752595819845</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>39.30426933952106</v>
+        <v>22.94835258676919</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -6479,10 +6479,10 @@
         <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>26.95781021091316</v>
+        <v>25.07187287105504</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>25.76596849795754</v>
       </c>
       <c r="D10" t="n">
-        <v>33.88011327355743</v>
+        <v>36.44247478164161</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>26.03594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>35.12202411942965</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>33.80157345721769</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>29.75873641112932</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.23984953947248</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>95.49459919208724</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.477496284224421</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.12183319752474</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.542809248696368</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
